--- a/workshop_prep/bob_version_successor_families_review.xlsx
+++ b/workshop_prep/bob_version_successor_families_review.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One row per Base+Gender franchise family with 2+ articles (i.e. a detected version succession, e.g. 'Astral GTX Jacket' -&gt; 'Astral GTX II Jacket'). 88 families found above the 200K SEK FY2025 family-sales threshold (config.MIN_FAMILY_SALES_FY25). Transition classified CLEAN CUTOVER (&lt;15% of family's 2025 units still on the older-looking article) / PARTIAL OVERLAP / HEAVY OVERLAP (&gt;35%) per config.classify_transition -- only computed for 2-article families; 3+ version families are flagged 'n/a, eyeball' since the old/new split is a simplification per analysis.py's own comment.</t>
+          <t>One row per Base+Gender franchise family with 2+ articles (i.e. a detected version succession, e.g. 'Astral GTX Jacket' -&gt; 'Astral GTX II Jacket'). 88 families found above the 200K SEK FY2025 family-sales threshold (config.MIN_FAMILY_SALES_FY25). CORRECTED METHODOLOGY (2026-07-31): predecessor vs. successor is now identified by version-token naming (II/III/IV/2.0 = successor, no token = predecessor), not by which article has fewer 2025 units. The prior heuristic silently inverted the label whenever a successor hadn't shipped any real 2025 volume yet (an unlaunched successor always has the fewest units), which wrongly classified 15 still-100%-predecessor families as CLEAN CUTOVER. Transition classified CLEAN CUTOVER (&lt;15% of family's 2025 units still on the predecessor article) / PARTIAL OVERLAP / HEAVY OVERLAP (&gt;35%) per config.classify_transition, now computed for every family (including former 3+-version 'eyeball' cases) by pooling all version-token articles as the successor side. Successor_Launched_2025 = the successor side had nonzero 2025 sales at all (a necessary condition for CLEAN CUTOVER to mean anything -- a family can only be a 'clean cutover' if a successor actually exists in the market). Successor_Sales_YTD26_SEK / Successor_YTD26_Pace_vs_OwnFY25 (successor's own YTD2026 sales as a %% of its own FY2025 sales, consistent with the ~40-44%% on-pace benchmark used elsewhere) are new columns added to flag families where the successor launched in 2025 but has gone near-zero in 2026 -- a stalled-transition risk distinct from the launch-timing bug above.</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Article-level detail behind the summary -- every article in every detected family, with its own 2024/2025 sales and units, for spot-checking whether the base-name+gender grouping is merging things correctly.</t>
+          <t>Article-level detail behind the summary -- every article in every detected family, with its own 2024/2025 sales and units, plus HasVersionToken (the field the corrected predecessor/successor split is now based on), for spot-checking whether the base-name+gender grouping is merging things correctly.</t>
         </is>
       </c>
     </row>
@@ -494,17 +494,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:P89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="37" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="27" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="13" max="13"/>
+    <col width="33" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,15 +543,55 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Likely_Outgoing_Article</t>
+          <t>Predecessor_Articles</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Outgoing_Share_of_2025_Units</t>
+          <t>Successor_Articles</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Predecessor_Sales2025_SEK</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Successor_Sales2025_SEK</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Predecessor_Share_of_2025_Units</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Successor_Launched_2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Successor_Sales_YTD26_SEK</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Predecessor_Sales_YTD26_SEK</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Successor_YTD26_Pace_vs_OwnFY25</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Articles_in_Family</t>
         </is>
@@ -576,10 +624,38 @@
           <t>Astral GTX Jacket Men</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Astral GTX II Jacket Men</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>6123093</v>
+      </c>
+      <c r="I2" t="n">
+        <v>11297751</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4925543</v>
+      </c>
+      <c r="M2" t="n">
+        <v>169825</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.4359755317673402</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Astral GTX II Jacket Men; Astral GTX Jacket Men</t>
         </is>
@@ -604,18 +680,43 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>Haglöfs Ridge GTX Low Men</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Haglöfs Ridge GTX II Low Men</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="n">
+        <v>11800605</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3239991</v>
+      </c>
+      <c r="M3" t="n">
+        <v>225974</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Hiking shoes</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Haglöfs Ridge GTX Low Men; Haglöfs Ridge GTX II Low Men</t>
         </is>
@@ -648,10 +749,38 @@
           <t>Astral GTX Jacket Women</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Astral GTX II Jacket Women</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4311356</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7412455</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3387543</v>
+      </c>
+      <c r="M4" t="n">
+        <v>635346</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4570068890806083</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Astral GTX II Jacket Women; Astral GTX Jacket Women</t>
         </is>
@@ -684,10 +813,38 @@
           <t>Front Proof Jacket Men</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Front Proof II Jacket Men</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>4320540</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5865630</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5349883</v>
+      </c>
+      <c r="M5" t="n">
+        <v>195141</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.9120730424523878</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Front Proof II Jacket Men; Front Proof Jacket Men</t>
         </is>
@@ -720,10 +877,38 @@
           <t>L.I.M GTX Jacket Men</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>L.I.M GTX II JacketMen</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>382086</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9714369</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3150681</v>
+      </c>
+      <c r="M6" t="n">
+        <v>51690</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.3243320281533469</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>L.I.M GTX II JacketMen; L.I.M GTX Jacket Men</t>
         </is>
@@ -748,18 +933,43 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Särna Mimic Hood Men</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Särna Mimic II HoodMen</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="n">
+        <v>8651449</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1006846</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1482506</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Särna Mimic Hood Men; Särna Mimic II HoodMen</t>
         </is>
@@ -784,18 +994,43 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Buteo Mid Jacket Men</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Buteo Mid II JacketMen</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="n">
+        <v>8038409</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>632278</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2571075</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Mid layer</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Buteo Mid Jacket Men; Buteo Mid II JacketMen</t>
         </is>
@@ -828,10 +1063,38 @@
           <t>Front Proof Jacket Women</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Front Proof II Jacket Women</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>3602967</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4031505</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2994993</v>
+      </c>
+      <c r="M9" t="n">
+        <v>760879</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.7428970074451104</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Front Proof II Jacket Women; Front Proof Jacket Women</t>
         </is>
@@ -856,18 +1119,43 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Särna Mimic Hood Women</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>Särna Mimic II HoodWomen</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" t="n">
+        <v>7346329</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>864294</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1374746</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Särna Mimic Hood Women; Särna Mimic II HoodWomen</t>
         </is>
@@ -900,10 +1188,38 @@
           <t>Long Down Parka Women</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Long Down II Parka Women</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1638696</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5227634</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1816</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>515530</v>
+      </c>
+      <c r="M11" t="n">
+        <v>363494</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.09861631476113286</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Long Down II Parka Women; Long Down Parka Women</t>
         </is>
@@ -928,18 +1244,43 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Haglöfs Ridge GTX Low Women</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>Haglöfs Ridge GTX II Low Women</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" t="n">
+        <v>5465945</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1058193</v>
+      </c>
+      <c r="M12" t="n">
+        <v>875672</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Hiking shoes</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Haglöfs Ridge GTX Low Women; Haglöfs Ridge GTX II Low Women</t>
         </is>
@@ -972,10 +1313,38 @@
           <t>L.I.M GTX Jacket Women</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>L.I.M GTX II JacketWomen</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>336521</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4964982</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0829</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2712505</v>
+      </c>
+      <c r="M13" t="n">
+        <v>98614</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5463272575811957</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>L.I.M GTX II JacketWomen; L.I.M GTX Jacket Women</t>
         </is>
@@ -1000,18 +1369,43 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>Buteo Mid Jacket Women</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Buteo Mid II JacketWomen</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" t="n">
+        <v>5108229</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>530158</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2204879</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Mid layer</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Buteo Mid Jacket Women; Buteo Mid II JacketWomen</t>
         </is>
@@ -1036,18 +1430,43 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>Haglöfs Ridge GTX Mid Men</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>Haglöfs Ridge GTX II Mid Men</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" t="n">
+        <v>4533678</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>599544</v>
+      </c>
+      <c r="M15" t="n">
+        <v>729162</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Trekking shoes</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Haglöfs Ridge GTX Mid Men; Haglöfs Ridge GTX II Mid Men</t>
         </is>
@@ -1080,10 +1499,38 @@
           <t>Vassi GTX Pro Jacket Men</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vassi GTX Pro II Jacket Men</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1601485</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2916874</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-4996</v>
+      </c>
+      <c r="M16" t="n">
+        <v>350661</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.001712792530633822</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Vassi GTX Pro II Jacket Men; Vassi GTX Pro Jacket Men</t>
         </is>
@@ -1116,10 +1563,38 @@
           <t>Salix Proof Mimic Parka Men</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Salix Proof Mimic II Parka Men</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>672346</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3571864</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.156</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>324026</v>
+      </c>
+      <c r="M17" t="n">
+        <v>68508</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.09071621987847242</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>Salix Proof Mimic II Parka Men; Salix Proof Mimic Parka Men</t>
         </is>
@@ -1144,18 +1619,43 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Kaja Proof Jacket Men</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Kaja Proof II Jacket Men</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" t="n">
+        <v>4201724</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>382010</v>
+      </c>
+      <c r="M18" t="n">
+        <v>848</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Kaja Proof Jacket Men; Kaja Proof II Jacket Men</t>
         </is>
@@ -1188,10 +1688,38 @@
           <t>Vassi GTX Jacket Men</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Vassi GTX II JacketMen</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1266516</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2639442</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>620142</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-92574</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.234951933022207</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Vassi GTX II JacketMen; Vassi GTX Jacket Men</t>
         </is>
@@ -1224,10 +1752,38 @@
           <t>Bield Down Hood Men</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bield Down II Hood Men</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>55591</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3793273</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>460</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0001212673066241212</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>Bield Down II Hood Men; Bield Down Hood Men</t>
         </is>
@@ -1252,18 +1808,46 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PARTIAL OVERLAP</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>Astral GTX Pant Women</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Astral GTX II Pant Women</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" t="n">
+        <v>2316156</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1407021</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.6883</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>379898</v>
+      </c>
+      <c r="M21" t="n">
+        <v>886892</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2700016559809697</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>Astral GTX Pant Women; Astral GTX II Pant Women</t>
         </is>
@@ -1296,10 +1880,38 @@
           <t>Vassi GTX Pro Bib Men</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Vassi GTX Pro II Bib Men</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1063812</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2639143</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>248069</v>
+      </c>
+      <c r="M22" t="n">
+        <v>125145</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.09399604341257749</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>Vassi GTX Pro II Bib Men; Vassi GTX Pro Bib Men</t>
         </is>
@@ -1332,10 +1944,38 @@
           <t>Astral GTX Pant Men</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Astral GTX II Pant Men</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1530630</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2166969</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4741</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>638084</v>
+      </c>
+      <c r="M23" t="n">
+        <v>461845</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.2944592193058599</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>Astral GTX II Pant Men; Astral GTX Pant Men</t>
         </is>
@@ -1360,7 +2000,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>n/a (3+ versions, eyeball)</t>
+          <t>CLEAN CUTOVER</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1368,10 +2008,38 @@
           <t>Puffy Mimic Hood Men</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Puffy Mimic III Hood Men; Puffy Mimic II HoodMen</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>249055</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3089308</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0629</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>480335</v>
+      </c>
+      <c r="M24" t="n">
+        <v>28996</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.1554830402148313</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>Puffy Mimic III Hood Men; Puffy Mimic II HoodMen; Puffy Mimic Hood Men</t>
         </is>
@@ -1404,10 +2072,38 @@
           <t>Vassi GTX Pant Men</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Vassi GTX II Pant Men</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1113923</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2045155</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>536194</v>
+      </c>
+      <c r="M25" t="n">
+        <v>264785</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.2621776833540734</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>Vassi GTX II Pant Men; Vassi GTX Pant Men</t>
         </is>
@@ -1440,10 +2136,38 @@
           <t>Chaos GTX Jacket Men</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chaos GTX II JacketMen</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>300493</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2835745</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2375931</v>
+      </c>
+      <c r="M26" t="n">
+        <v>112926</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.837850723531206</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>Chaos GTX II JacketMen; Chaos GTX Jacket Men</t>
         </is>
@@ -1468,18 +2192,43 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>Haglöfs Ridge GTX Mid Women</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>Haglöfs Ridge GTX II Mid Women</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" t="n">
+        <v>3066414</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>400598</v>
+      </c>
+      <c r="M27" t="n">
+        <v>417508</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Trekking shoes</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>Haglöfs Ridge GTX Mid Women; Haglöfs Ridge GTX II Mid Women</t>
         </is>
@@ -1512,10 +2261,38 @@
           <t>Chaos GTX Jacket Women</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Chaos GTX II JacketWomen</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>749867</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2223092</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1470721</v>
+      </c>
+      <c r="M28" t="n">
+        <v>96153</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.6615655132581107</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>Chaos GTX II JacketWomen; Chaos GTX Jacket Women</t>
         </is>
@@ -1540,18 +2317,46 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PARTIAL OVERLAP</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
+          <t>L.I.M Mimic Hood Men</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
           <t>L.I.M Mimic II HoodMen</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" t="n">
+        <v>2158170</v>
+      </c>
+      <c r="I29" t="n">
+        <v>701822</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.7778</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>232409</v>
+      </c>
+      <c r="M29" t="n">
+        <v>205115</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.331150918608992</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>L.I.M Mimic Hood Men; L.I.M Mimic II HoodMen</t>
         </is>
@@ -1576,18 +2381,46 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>n/a (3+ versions, eyeball)</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Long Mimic II ParkaWomen</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>-0.259</v>
-      </c>
-      <c r="H30" t="inlineStr">
+          <t>Long Mimic Parka Women</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Long Mimic III Parka Women; Long Mimic II ParkaWomen</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>925463</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1716942</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>979200</v>
+      </c>
+      <c r="M30" t="n">
+        <v>128310</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.5703162949010508</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>Long Mimic III Parka Women; Long Mimic Parka Women; Long Mimic II ParkaWomen</t>
         </is>
@@ -1620,10 +2453,38 @@
           <t>L.I.M Down Hood Men</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>L.I.M Down II Hood Men</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1316909</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1295953</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4609</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>701596</v>
+      </c>
+      <c r="M31" t="n">
+        <v>61478</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.541374571454366</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>L.I.M Down II Hood Men; L.I.M Down Hood Men</t>
         </is>
@@ -1656,10 +2517,38 @@
           <t>L.I.M Fuse Pant Men</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0.453</v>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>L.I.M Fuse II Pant Men</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1117926</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1236398</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>691085</v>
+      </c>
+      <c r="M32" t="n">
+        <v>377300</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.5589502732938746</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Legwear</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>L.I.M Fuse II Pant Men; L.I.M Fuse Pant Men</t>
         </is>
@@ -1692,10 +2581,38 @@
           <t>Vassi GTX Jacket Women</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Vassi GTX II JacketWomen</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1041755</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1270625</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>331477</v>
+      </c>
+      <c r="M33" t="n">
+        <v>312764</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.2608771273979341</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>Vassi GTX II JacketWomen; Vassi GTX Jacket Women</t>
         </is>
@@ -1728,10 +2645,38 @@
           <t>Vassi GTX Pro Jacket Women</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>0.426</v>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Vassi GTX Pro II Jacket Women</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>911554</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1216944</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>148614</v>
+      </c>
+      <c r="M34" t="n">
+        <v>514729</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.1221206563325839</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>Vassi GTX Pro II Jacket Women; Vassi GTX Pro Jacket Women</t>
         </is>
@@ -1764,10 +2709,38 @@
           <t>L.I.M Fuse Shorts Men</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>L.I.M Fuse II Shorts Men</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>806806</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1308675</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.4057</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>936624</v>
+      </c>
+      <c r="M35" t="n">
+        <v>184982</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.7157040518081266</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Legwear</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>L.I.M Fuse II Shorts Men; L.I.M Fuse Shorts Men</t>
         </is>
@@ -1797,13 +2770,41 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>L.I.M Fuse Pant Women</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
           <t>L.I.M Fuse II Pant Women</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" t="n">
+        <v>1105882</v>
+      </c>
+      <c r="I36" t="n">
+        <v>917902</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5121</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>680459</v>
+      </c>
+      <c r="M36" t="n">
+        <v>464283</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.7413198794642565</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Legwear</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>L.I.M Fuse Pant Women; L.I.M Fuse II Pant Women</t>
         </is>
@@ -1836,10 +2837,38 @@
           <t>Vassi GTX Pro Bib Women</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Vassi GTX Pro II Bib Women</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>781665</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1218578</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>228498</v>
+      </c>
+      <c r="M37" t="n">
+        <v>260458</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.1875120016937775</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>Vassi GTX Pro II Bib Women; Vassi GTX Pro Bib Women</t>
         </is>
@@ -1872,10 +2901,38 @@
           <t>Salix Proof Mimic Parka Women</t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Salix Proof Mimic II Parka Women</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>512279</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1456929</v>
+      </c>
+      <c r="J38" t="n">
         <v>0.242</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>132770</v>
+      </c>
+      <c r="M38" t="n">
+        <v>43162</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.09113004134038104</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>Salix Proof Mimic II Parka Women; Salix Proof Mimic Parka Women</t>
         </is>
@@ -1908,10 +2965,38 @@
           <t>Bield Down Hood Women</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="H39" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bield Down II Hood Women</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>312795</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1627659</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.1561</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>8920</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>Bield Down II Hood Women; Bield Down Hood Women</t>
         </is>
@@ -1936,18 +3021,46 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PARTIAL OVERLAP</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
+          <t>L.I.M Mimic Hood Women</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>L.I.M Mimic II HoodWomen</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" t="n">
+        <v>1348064</v>
+      </c>
+      <c r="I40" t="n">
+        <v>477894</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.7401</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>159803</v>
+      </c>
+      <c r="M40" t="n">
+        <v>184616</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.3343900530243109</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>L.I.M Mimic Hood Women; L.I.M Mimic II HoodWomen</t>
         </is>
@@ -1980,10 +3093,38 @@
           <t>Vassi GTX Pant Women</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Vassi GTX II Pant Women</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>627959</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1033627</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>316892</v>
+      </c>
+      <c r="M41" t="n">
+        <v>395037</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.3065825486369841</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>Vassi GTX II Pant Women; Vassi GTX Pant Women</t>
         </is>
@@ -2016,10 +3157,38 @@
           <t>L.I.M Fuse Shorts Women</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>L.I.M Fuse II Shorts Women</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>569742</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1076786</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>675582</v>
+      </c>
+      <c r="M42" t="n">
+        <v>196328</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.6274060026783409</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Legwear</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
         <is>
           <t>L.I.M Fuse II Shorts Women; L.I.M Fuse Shorts Women</t>
         </is>
@@ -2044,18 +3213,46 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PARTIAL OVERLAP</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>L.I.M Alpha Hood Men</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>L.I.M Alpha II HoodMen</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>0.259</v>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" t="n">
+        <v>1271961</v>
+      </c>
+      <c r="I43" t="n">
+        <v>369680</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>143423</v>
+      </c>
+      <c r="M43" t="n">
+        <v>113212</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.3879652672581692</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>L.I.M Alpha Hood Men; L.I.M Alpha II HoodMen</t>
         </is>
@@ -2088,10 +3285,38 @@
           <t>L.I.M Mid Multi Hood Men</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>L.I.M Mid Multi II Hood Men</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>472040</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1167774</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>808135</v>
+      </c>
+      <c r="M44" t="n">
+        <v>43037</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.6920303072341052</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Mid layer</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>L.I.M Mid Multi II Hood Men; L.I.M Mid Multi Hood Men</t>
         </is>
@@ -2121,13 +3346,41 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>L.I.M Down Hood Women</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>L.I.M Down II Hood Women</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>0.448</v>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" t="n">
+        <v>869409</v>
+      </c>
+      <c r="I45" t="n">
+        <v>618168</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.5518999999999999</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>417174</v>
+      </c>
+      <c r="M45" t="n">
+        <v>350241</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.6748553791202392</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
         <is>
           <t>L.I.M Down Hood Women; L.I.M Down II Hood Women</t>
         </is>
@@ -2157,13 +3410,41 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>L.I.M Down Jacket Men</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
           <t>L.I.M Down II Jacket Men</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" t="n">
+        <v>926599</v>
+      </c>
+      <c r="I46" t="n">
+        <v>540417</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.5718</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>196246</v>
+      </c>
+      <c r="M46" t="n">
+        <v>54964</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.3631380952116606</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>L.I.M Down Jacket Men; L.I.M Down II Jacket Men</t>
         </is>
@@ -2196,10 +3477,38 @@
           <t>Riksgränsen Down 850 Hood Men</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H47" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Riksgränsen Down 850 II Hood Men</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>533942</v>
+      </c>
+      <c r="I47" t="n">
+        <v>910695</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>167308</v>
+      </c>
+      <c r="M47" t="n">
+        <v>163681</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.183714635525615</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
         <is>
           <t>Riksgränsen Down 850 II Hood Men; Riksgränsen Down 850 Hood Men</t>
         </is>
@@ -2232,10 +3541,38 @@
           <t>L.I.M Mid Multi Hood Women</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="H48" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>L.I.M Mid Multi II Hood Women</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>404315</v>
+      </c>
+      <c r="I48" t="n">
+        <v>881849</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>617864</v>
+      </c>
+      <c r="M48" t="n">
+        <v>56232</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.7006460289686783</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Mid layer</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
         <is>
           <t>L.I.M Mid Multi II Hood Women; L.I.M Mid Multi Hood Women</t>
         </is>
@@ -2260,18 +3597,46 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>Bow Windstopper Glove</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
           <t>Bow Windstopper II Glove</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" t="n">
+        <v>956326</v>
+      </c>
+      <c r="I49" t="n">
+        <v>269243</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8585</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>260185</v>
+      </c>
+      <c r="M49" t="n">
+        <v>-386268</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.9663575283294273</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
         <is>
           <t>Bow Windstopper Glove; Bow Windstopper II Glove</t>
         </is>
@@ -2301,13 +3666,41 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>Korp Proof Pant Men</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
           <t>Korp Proof II Pant Men</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" t="n">
+        <v>733412</v>
+      </c>
+      <c r="I50" t="n">
+        <v>476787</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.5504</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>594318</v>
+      </c>
+      <c r="M50" t="n">
+        <v>27872</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1.246506301556041</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>Korp Proof Pant Men; Korp Proof II Pant Men</t>
         </is>
@@ -2332,18 +3725,46 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PARTIAL OVERLAP</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>Lite Standard Zip-Off Pant Men</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
           <t>Lite Standard Zip-Off II Pant Men</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" t="n">
+        <v>1107833</v>
+      </c>
+      <c r="I51" t="n">
+        <v>97114</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.8258</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1306260</v>
+      </c>
+      <c r="M51" t="n">
+        <v>98338</v>
+      </c>
+      <c r="N51" t="n">
+        <v>13.45078979343864</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Legwear</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
         <is>
           <t>Lite Standard Zip-Off Pant Men; Lite Standard Zip-Off II Pant Men</t>
         </is>
@@ -2376,10 +3797,38 @@
           <t>Gran 3-in-1 Proof Jacket Men</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H52" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Gran 3-in-1 Proof II Jacket Men</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>213850</v>
+      </c>
+      <c r="I52" t="n">
+        <v>976727</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.1405</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>13805</v>
+      </c>
+      <c r="M52" t="n">
+        <v>16800</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.01413393916621533</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
         <is>
           <t>Gran 3-in-1 Proof II Jacket Men; Gran 3-in-1 Proof Jacket Men</t>
         </is>
@@ -2412,10 +3861,38 @@
           <t>L.I.M Mid Fast HoodMen</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="H53" t="inlineStr">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>L.I.M Mid Fast II Hood Men</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>533639</v>
+      </c>
+      <c r="I53" t="n">
+        <v>654238</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.4745</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>173265</v>
+      </c>
+      <c r="M53" t="n">
+        <v>82459</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.2648348154647086</v>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Mid layer</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
         <is>
           <t>L.I.M Mid Fast II Hood Men; L.I.M Mid Fast HoodMen</t>
         </is>
@@ -2440,18 +3917,43 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>Haglöfs Krusa GTX Low Women</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>Haglöfs Krusa GTX II Low Women</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" t="n">
+        <v>1175486</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>535600</v>
+      </c>
+      <c r="M54" t="n">
+        <v>444104</v>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Hiking shoes</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
         <is>
           <t>Haglöfs Krusa GTX Low Women; Haglöfs Krusa GTX II Low Women</t>
         </is>
@@ -2484,10 +3986,38 @@
           <t>Chaos GTX Pant Women</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="H55" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Chaos GTX II Pant Women</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>235818</v>
+      </c>
+      <c r="I55" t="n">
+        <v>916462</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.2047</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>759497</v>
+      </c>
+      <c r="M55" t="n">
+        <v>29140</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.8287272140034175</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
         <is>
           <t>Chaos GTX II Pant Women; Chaos GTX Pant Women</t>
         </is>
@@ -2520,10 +4050,38 @@
           <t>Chaos GTX Pant Men</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="H56" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Chaos GTX II Pant Men</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>173830</v>
+      </c>
+      <c r="I56" t="n">
+        <v>912538</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.1408</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>769347</v>
+      </c>
+      <c r="M56" t="n">
+        <v>23214</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.8430848907114005</v>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
         <is>
           <t>Chaos GTX II Pant Men; Chaos GTX Pant Men</t>
         </is>
@@ -2553,13 +4111,41 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>Korp Proof Pant Women</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>Korp Proof II Pant Women</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" t="n">
+        <v>642781</v>
+      </c>
+      <c r="I57" t="n">
+        <v>435941</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.5872000000000001</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>458220</v>
+      </c>
+      <c r="M57" t="n">
+        <v>57794</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1.051105539511081</v>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
         <is>
           <t>Korp Proof Pant Women; Korp Proof II Pant Women</t>
         </is>
@@ -2584,18 +4170,43 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>Lite Standard Zip-Off Pant Women</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>Lite Standard Zip-Off II Pant Women</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" t="n">
+        <v>1018734</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1120314</v>
+      </c>
+      <c r="M58" t="n">
+        <v>189571</v>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Legwear</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
         <is>
           <t>Lite Standard Zip-Off Pant Women; Lite Standard Zip-Off II Pant Women</t>
         </is>
@@ -2620,18 +4231,43 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>Vandra Pant Women</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
           <t>Vandra II Pant Women</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" t="n">
+        <v>964308</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
         <is>
           <t>Vandra Pant Women; Vandra II Pant Women</t>
         </is>
@@ -2661,13 +4297,41 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>L.I.M Mid Fast HoodWomen</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
           <t>L.I.M Mid Fast II Hood Women</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" t="n">
+        <v>513876</v>
+      </c>
+      <c r="I60" t="n">
+        <v>379465</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.6085</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>61283</v>
+      </c>
+      <c r="M60" t="n">
+        <v>160471</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.1614984254147286</v>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Mid layer</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
         <is>
           <t>L.I.M Mid Fast HoodWomen; L.I.M Mid Fast II Hood Women</t>
         </is>
@@ -2700,10 +4364,38 @@
           <t>Fiction Down Hood Men</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="H61" t="inlineStr">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Fiction Down II Hood Men</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>59270</v>
+      </c>
+      <c r="I61" t="n">
+        <v>813427</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.0447</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>9395</v>
+      </c>
+      <c r="M61" t="n">
+        <v>-1020</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.01154989937634231</v>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t>Fiction Down II Hood Men; Fiction Down Hood Men</t>
         </is>
@@ -2736,10 +4428,38 @@
           <t>Base Mimic Hood Men</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="inlineStr">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Base Mimic II Hood Men</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>855190</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
         <is>
           <t>Base Mimic II Hood Men; Base Mimic Hood Men</t>
         </is>
@@ -2772,10 +4492,38 @@
           <t>Mountain Cap</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="H63" t="inlineStr">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Mountain II Cap</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>103259</v>
+      </c>
+      <c r="I63" t="n">
+        <v>745523</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="K63" t="b">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>182983</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1507</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.2454424611983802</v>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Accessories</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t>Mountain II Cap; Mountain Cap</t>
         </is>
@@ -2808,10 +4556,38 @@
           <t>Riksgränsen Down 850 Hood Women</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="H64" t="inlineStr">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Riksgränsen Down 850 II Hood Women</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>398390</v>
+      </c>
+      <c r="I64" t="n">
+        <v>434759</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="K64" t="b">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>35427</v>
+      </c>
+      <c r="M64" t="n">
+        <v>377195</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.08148652471829221</v>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
         <is>
           <t>Riksgränsen Down 850 II Hood Women; Riksgränsen Down 850 Hood Women</t>
         </is>
@@ -2844,10 +4620,38 @@
           <t>Puffy Mimic Hood Women</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>0.316</v>
-      </c>
-      <c r="H65" t="inlineStr">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Puffy Mimic II HoodWomen</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>278545</v>
+      </c>
+      <c r="I65" t="n">
+        <v>546244</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="K65" t="b">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>54290</v>
+      </c>
+      <c r="M65" t="n">
+        <v>16606</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.0993878193627756</v>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t>Puffy Mimic II HoodWomen; Puffy Mimic Hood Women</t>
         </is>
@@ -2872,18 +4676,46 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PARTIAL OVERLAP</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
+          <t>L.I.M Alpha Hood Women</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
           <t>L.I.M Alpha II HoodWomen</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" t="n">
+        <v>677197</v>
+      </c>
+      <c r="I66" t="n">
+        <v>142550</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.7821</v>
+      </c>
+      <c r="K66" t="b">
+        <v>1</v>
+      </c>
+      <c r="L66" t="n">
+        <v>121017</v>
+      </c>
+      <c r="M66" t="n">
+        <v>265446</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.8489442300947037</v>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
         <is>
           <t>L.I.M Alpha Hood Women; L.I.M Alpha II HoodWomen</t>
         </is>
@@ -2916,10 +4748,38 @@
           <t>Essens Down Hood Women</t>
         </is>
       </c>
-      <c r="G67" t="n">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Essens Down II HoodWomen</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>893</v>
+      </c>
+      <c r="I67" t="n">
+        <v>816725</v>
+      </c>
+      <c r="J67" t="n">
         <v>0.003</v>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="K67" t="b">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-5230</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1392</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-0.006403624230922281</v>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>Essens Down II HoodWomen; Essens Down Hood Women</t>
         </is>
@@ -2952,10 +4812,38 @@
           <t>Base Mimic Hood Women</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="inlineStr">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Base Mimic II Hood Women</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>791678</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="b">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
         <is>
           <t>Base Mimic II Hood Women; Base Mimic Hood Women</t>
         </is>
@@ -2980,18 +4868,46 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
+          <t>Zircon Shorts Men</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
           <t>Zircon 2.0 Shorts Men</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" t="n">
+        <v>687615</v>
+      </c>
+      <c r="I69" t="n">
+        <v>24632</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.9754</v>
+      </c>
+      <c r="K69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>64829</v>
+      </c>
+      <c r="M69" t="n">
+        <v>840</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2.631901591425788</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Legwear</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
         <is>
           <t>Zircon Shorts Men; Zircon 2.0 Shorts Men</t>
         </is>
@@ -3016,18 +4932,46 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
+          <t>L.I.M Mimic Vest Men</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
           <t>L.I.M Mimic II VestMen</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" t="n">
+        <v>682249</v>
+      </c>
+      <c r="I70" t="n">
+        <v>521</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>90427</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
         <is>
           <t>L.I.M Mimic Vest Men; L.I.M Mimic II VestMen</t>
         </is>
@@ -3060,10 +5004,38 @@
           <t>L.I.M Critus Pant Men</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H71" t="inlineStr">
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>L.I.M Critus II Pant Men</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>19824</v>
+      </c>
+      <c r="I71" t="n">
+        <v>633946</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="K71" t="b">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>640</v>
+      </c>
+      <c r="M71" t="n">
+        <v>3837</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.001009549709281232</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
         <is>
           <t>L.I.M Critus II Pant Men; L.I.M Critus Pant Men</t>
         </is>
@@ -3096,10 +5068,38 @@
           <t>Mila Jacket Men</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="H72" t="inlineStr">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Mila II Jacket Men</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>-3302</v>
+      </c>
+      <c r="I72" t="n">
+        <v>638616</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="K72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>125105</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-2571</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.1959001966753104</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
         <is>
           <t>Mila II Jacket Men; Mila Jacket Men</t>
         </is>
@@ -3124,18 +5124,43 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>Zircon Shorts Women</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
           <t>Zircon 2.0 Shorts Women</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" t="n">
+        <v>610199</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>10578</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Legwear</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
         <is>
           <t>Zircon Shorts Women; Zircon 2.0 Shorts Women</t>
         </is>
@@ -3168,10 +5193,38 @@
           <t>L.I.M Critus Pant Women</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" t="inlineStr">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>L.I.M Critus II Pant Women</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>609331</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-1118</v>
+      </c>
+      <c r="M74" t="n">
+        <v>2352</v>
+      </c>
+      <c r="N74" t="n">
+        <v>-0.00183479914857442</v>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
         <is>
           <t>L.I.M Critus II Pant Women; L.I.M Critus Pant Women</t>
         </is>
@@ -3196,18 +5249,46 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PARTIAL OVERLAP</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
+          <t>Husk Jacket Junior</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>Husk Jacket II Junior</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" t="n">
+        <v>469060</v>
+      </c>
+      <c r="I75" t="n">
+        <v>136250</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.8328</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>153685</v>
+      </c>
+      <c r="M75" t="n">
+        <v>212138</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1.127963302752294</v>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
         <is>
           <t>Husk Jacket Junior; Husk Jacket II Junior</t>
         </is>
@@ -3240,10 +5321,38 @@
           <t>Mila Jacket Women</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="H76" t="inlineStr">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Mila II Jacket Women</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>54713</v>
+      </c>
+      <c r="I76" t="n">
+        <v>439965</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.1165</v>
+      </c>
+      <c r="K76" t="b">
+        <v>1</v>
+      </c>
+      <c r="L76" t="n">
+        <v>151519</v>
+      </c>
+      <c r="M76" t="n">
+        <v>-1714</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.3443887581966747</v>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
         <is>
           <t>Mila II Jacket Women; Mila Jacket Women</t>
         </is>
@@ -3276,10 +5385,38 @@
           <t>L.I.M Mimic 3/4 Pant Men</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="H77" t="inlineStr">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>L.I.M Mimic II 3/4 Pant Men</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>216365</v>
+      </c>
+      <c r="I77" t="n">
+        <v>253642</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="K77" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>94819</v>
+      </c>
+      <c r="M77" t="n">
+        <v>24223</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.3738300439201709</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
         <is>
           <t>L.I.M Mimic II 3/4 Pant Men; L.I.M Mimic 3/4 Pant Men</t>
         </is>
@@ -3304,18 +5441,46 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
+          <t>L.I.M Down Jacket Women</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
           <t>L.I.M Down II Jacket Women</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78" t="n">
+        <v>452560</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2654</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.9905</v>
+      </c>
+      <c r="K78" t="b">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>66195</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
         <is>
           <t>L.I.M Down Jacket Women; L.I.M Down II Jacket Women</t>
         </is>
@@ -3340,18 +5505,43 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>Mid Flex Pant Men</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>Mid II Flex Pant Men</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79" t="n">
+        <v>436870</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>27704</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Legwear</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t>Mid Flex Pant Men; Mid II Flex Pant Men</t>
         </is>
@@ -3376,18 +5566,46 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>Front Proof Pant Men</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
           <t>Front Proof II PantMen</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" t="n">
+        <v>409235</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1204</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.9969</v>
+      </c>
+      <c r="K80" t="b">
+        <v>1</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>33324</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
         <is>
           <t>Front Proof Pant Men; Front Proof II PantMen</t>
         </is>
@@ -3417,13 +5635,41 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
+          <t>L.I.M Mimic 3/4 Pant Women</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
           <t>L.I.M Mimic II 3/4 Pant Women</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" t="n">
+        <v>243137</v>
+      </c>
+      <c r="I81" t="n">
+        <v>141854</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.6342</v>
+      </c>
+      <c r="K81" t="b">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>74504</v>
+      </c>
+      <c r="M81" t="n">
+        <v>57329</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.5252160672240472</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
         <is>
           <t>L.I.M Mimic 3/4 Pant Women; L.I.M Mimic II 3/4 Pant Women</t>
         </is>
@@ -3448,18 +5694,46 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PARTIAL OVERLAP</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>Husk Pant Junior</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
           <t>Husk Pant II Junior</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="H82" t="inlineStr">
+      <c r="H82" t="n">
+        <v>237463</v>
+      </c>
+      <c r="I82" t="n">
+        <v>101154</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.7891</v>
+      </c>
+      <c r="K82" t="b">
+        <v>1</v>
+      </c>
+      <c r="L82" t="n">
+        <v>113694</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1.123969393202444</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
         <is>
           <t>Husk Pant Junior; Husk Pant II Junior</t>
         </is>
@@ -3492,10 +5766,38 @@
           <t>Mimic Skirt Women</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>0.268</v>
-      </c>
-      <c r="H83" t="inlineStr">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Mimic II Skirt Women</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>71616</v>
+      </c>
+      <c r="I83" t="n">
+        <v>208160</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.2684</v>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
+      </c>
+      <c r="L83" t="n">
+        <v>22432</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2698</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0.1077632590315142</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
         <is>
           <t>Mimic II Skirt Women; Mimic Skirt Women</t>
         </is>
@@ -3528,10 +5830,38 @@
           <t>Mila Rain Pant Women</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="H84" t="inlineStr">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Mila Rain II Pant Women</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>-1972</v>
+      </c>
+      <c r="I84" t="n">
+        <v>278611</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-0.0065</v>
+      </c>
+      <c r="K84" t="b">
+        <v>1</v>
+      </c>
+      <c r="L84" t="n">
+        <v>134486</v>
+      </c>
+      <c r="M84" t="n">
+        <v>-1230</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.4827016880166253</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
         <is>
           <t>Mila Rain II Pant Women; Mila Rain Pant Women</t>
         </is>
@@ -3564,10 +5894,38 @@
           <t>Mila Rain Pant Men</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="H85" t="inlineStr">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Mila Rain II Pant Men</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>8428</v>
+      </c>
+      <c r="I85" t="n">
+        <v>265903</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="K85" t="b">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>136132</v>
+      </c>
+      <c r="M85" t="n">
+        <v>2376</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.5119611286822638</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>Mila Rain II Pant Men; Mila Rain Pant Men</t>
         </is>
@@ -3592,18 +5950,46 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
+          <t>L.I.M Mimic Vest Women</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
           <t>L.I.M Mimic II VestWomen</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86" t="n">
+        <v>256562</v>
+      </c>
+      <c r="I86" t="n">
+        <v>521</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="K86" t="b">
+        <v>1</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>144471</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Insulation</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
         <is>
           <t>L.I.M Mimic Vest Women; L.I.M Mimic II VestWomen</t>
         </is>
@@ -3628,18 +6014,46 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
+          <t>Aero Pant Men</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
           <t>Aero II Pant Men</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" t="n">
+        <v>248341</v>
+      </c>
+      <c r="I87" t="n">
+        <v>-799</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="K87" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>157557</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t>Aero Pant Men; Aero II Pant Men</t>
         </is>
@@ -3669,13 +6083,41 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
+          <t>L.I.M ZT Air Base Men</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
           <t>L.I.M ZT II Air Base Men</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88" t="n">
+        <v>96112</v>
+      </c>
+      <c r="I88" t="n">
+        <v>135781</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="K88" t="b">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>32968</v>
+      </c>
+      <c r="M88" t="n">
+        <v>23317</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.2428027485436107</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Base layer</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
         <is>
           <t>L.I.M ZT Air Base Men; L.I.M ZT II Air Base Men</t>
         </is>
@@ -3700,18 +6142,43 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CLEAN CUTOVER</t>
+          <t>HEAVY OVERLAP</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>L.I.M Jacket Women</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>L.I.M III Jacket Women</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" t="n">
+        <v>216081</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>18180</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
         <is>
           <t>L.I.M Jacket Women; L.I.M III Jacket Women</t>
         </is>
@@ -3734,12 +6201,12 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3760,32 +6227,32 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>HasVersionToken</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Sales_2024_SEK</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Units_2024</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sales_2025_SEK</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Units_2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>FamilySales2025_SEK</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ShareOfFamilyUnits2025</t>
         </is>
       </c>
     </row>
@@ -3805,23 +6272,23 @@
           <t>Astral GTX II Jacket Men</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
         <v>1770</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
       <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
         <v>11297751</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>6940</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>17420844</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.646</v>
       </c>
     </row>
     <row r="3">
@@ -3840,23 +6307,23 @@
           <t>Astral GTX Jacket Men</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
         <v>13836667</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>8272</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>6123093</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>3811</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>17420844</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.354</v>
       </c>
     </row>
     <row r="4">
@@ -3875,23 +6342,23 @@
           <t>Haglöfs Ridge GTX Low Men</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
         <v>11207820</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>14816</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>11800605</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>14864</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>11800605</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3910,8 +6377,8 @@
           <t>Haglöfs Ridge GTX II Low Men</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
+      <c r="D5" t="b">
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -3923,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>11800605</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3945,23 +6412,23 @@
           <t>Astral GTX II Jacket Women</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
         <v>-1329</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-1</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>7412455</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>4577</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>11723811</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.611</v>
       </c>
     </row>
     <row r="7">
@@ -3980,23 +6447,23 @@
           <t>Astral GTX Jacket Women</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>9089666</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>5386</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>4311356</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>2913</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>11723811</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.389</v>
       </c>
     </row>
     <row r="8">
@@ -4015,23 +6482,23 @@
           <t>Front Proof II Jacket Men</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>2492</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>5865630</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>5542</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>10186169</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.594</v>
       </c>
     </row>
     <row r="9">
@@ -4050,23 +6517,23 @@
           <t>Front Proof Jacket Men</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>6121938</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>5253</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>4320540</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>3787</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>10186169</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.406</v>
       </c>
     </row>
     <row r="10">
@@ -4085,23 +6552,23 @@
           <t>L.I.M GTX II JacketMen</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>10023745</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>8495</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>9714369</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>7106</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>10096455</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.949</v>
       </c>
     </row>
     <row r="11">
@@ -4120,23 +6587,23 @@
           <t>L.I.M GTX Jacket Men</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
         <v>5872092</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>6816</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>382086</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>380</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>10096455</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.051</v>
       </c>
     </row>
     <row r="12">
@@ -4155,23 +6622,23 @@
           <t>Särna Mimic Hood Men</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
         <v>8051096</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>10975</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>8651449</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>12104</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>8651449</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -4190,8 +6657,8 @@
           <t>Särna Mimic II HoodMen</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
+      <c r="D13" t="b">
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4203,10 +6670,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>8651449</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4225,23 +6692,23 @@
           <t>Buteo Mid Jacket Men</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
         <v>8148833</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>26352</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>8038409</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>27319</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>8038409</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -4260,8 +6727,8 @@
           <t>Buteo Mid II JacketMen</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
+      <c r="D15" t="b">
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -4273,10 +6740,10 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>8038409</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4295,23 +6762,23 @@
           <t>Front Proof II Jacket Women</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
         <v>2492</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>4031505</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>3808</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>7634472</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.516</v>
       </c>
     </row>
     <row r="17">
@@ -4330,23 +6797,23 @@
           <t>Front Proof Jacket Women</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
         <v>3752887</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>3195</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>3602967</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>3577</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>7634472</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.484</v>
       </c>
     </row>
     <row r="18">
@@ -4365,23 +6832,23 @@
           <t>Särna Mimic Hood Women</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
         <v>5693185</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>7975</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>7346329</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>10268</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>7346329</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -4400,8 +6867,8 @@
           <t>Särna Mimic II HoodWomen</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
+      <c r="D19" t="b">
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4413,10 +6880,10 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>7346329</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4435,23 +6902,23 @@
           <t>Long Down II Parka Women</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
+      <c r="D20" t="b">
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>5227634</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>3460</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>6866331</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -4470,23 +6937,23 @@
           <t>Long Down Parka Women</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
         <v>6085452</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>3379</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>1638696</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>768</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>6866331</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.182</v>
       </c>
     </row>
     <row r="22">
@@ -4505,23 +6972,23 @@
           <t>Haglöfs Ridge GTX Low Women</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
         <v>4460615</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>6069</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>5465945</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>6690</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>5465945</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -4540,8 +7007,8 @@
           <t>Haglöfs Ridge GTX II Low Women</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>0</v>
+      <c r="D23" t="b">
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4553,10 +7020,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>5465945</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4575,23 +7042,23 @@
           <t>L.I.M GTX II JacketWomen</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
         <v>7219945</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>6200</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>4964982</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>4051</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>5301503</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.917</v>
       </c>
     </row>
     <row r="25">
@@ -4610,23 +7077,23 @@
           <t>L.I.M GTX Jacket Women</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
         <v>5501235</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>6780</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>336521</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>366</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>5301503</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.083</v>
       </c>
     </row>
     <row r="26">
@@ -4645,23 +7112,23 @@
           <t>Buteo Mid Jacket Women</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
         <v>5078398</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>16270</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>5108229</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>17832</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>5108229</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -4680,8 +7147,8 @@
           <t>Buteo Mid II JacketWomen</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>0</v>
+      <c r="D27" t="b">
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -4693,10 +7160,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
         <v>5108229</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4715,23 +7182,23 @@
           <t>Haglöfs Ridge GTX Mid Men</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
         <v>2661132</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>2962</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>4533678</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>4449</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>4533678</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -4750,8 +7217,8 @@
           <t>Haglöfs Ridge GTX II Mid Men</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
+      <c r="D29" t="b">
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -4763,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>4533678</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -4785,23 +7252,23 @@
           <t>Vassi GTX Pro II Jacket Men</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
         <v>5957</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>2</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>2916874</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>882</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>4518358</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.671</v>
       </c>
     </row>
     <row r="31">
@@ -4820,23 +7287,23 @@
           <t>Vassi GTX Pro Jacket Men</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
         <v>2887676</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>783</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>1601485</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>432</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>4518358</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.329</v>
       </c>
     </row>
     <row r="32">
@@ -4855,23 +7322,23 @@
           <t>Salix Proof Mimic II Parka Men</t>
         </is>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
+      <c r="D32" t="b">
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
         <v>3571864</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>3435</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>4244210</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.844</v>
       </c>
     </row>
     <row r="33">
@@ -4890,23 +7357,23 @@
           <t>Salix Proof Mimic Parka Men</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
         <v>3350649</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>3079</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>672346</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>635</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>4244210</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.156</v>
       </c>
     </row>
     <row r="34">
@@ -4925,23 +7392,23 @@
           <t>Kaja Proof Jacket Men</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" t="b">
         <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
         <v>4201724</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>5508</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>4201724</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -4960,8 +7427,8 @@
           <t>Kaja Proof II Jacket Men</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>0</v>
+      <c r="D35" t="b">
+        <v>1</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -4973,10 +7440,10 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>4201724</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4995,23 +7462,23 @@
           <t>Vassi GTX II JacketMen</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
         <v>10218</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>5</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>2639442</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>1116</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>3905958</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.74</v>
       </c>
     </row>
     <row r="37">
@@ -5030,23 +7497,23 @@
           <t>Vassi GTX Jacket Men</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
         <v>4232120</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>1487</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>1266516</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>393</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>3905958</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.26</v>
       </c>
     </row>
     <row r="38">
@@ -5065,23 +7532,23 @@
           <t>Bield Down II Hood Men</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>0</v>
+      <c r="D38" t="b">
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
         <v>3793273</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>4562</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>3848865</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.985</v>
       </c>
     </row>
     <row r="39">
@@ -5100,23 +7567,23 @@
           <t>Bield Down Hood Men</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
         <v>2927869</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>3373</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>55591</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>71</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>3848865</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.015</v>
       </c>
     </row>
     <row r="40">
@@ -5135,23 +7602,23 @@
           <t>Astral GTX Pant Women</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
         <v>1705261</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>1661</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>2316156</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>2743</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>3723177</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -5170,23 +7637,23 @@
           <t>Astral GTX II Pant Women</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
         <v>-827</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>-1</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>1407021</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>1242</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>3723177</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.312</v>
       </c>
     </row>
     <row r="42">
@@ -5205,23 +7672,23 @@
           <t>Vassi GTX Pro II Bib Men</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
         <v>2255</v>
       </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
       <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
         <v>2639143</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>960</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>3702955</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.747</v>
       </c>
     </row>
     <row r="43">
@@ -5240,23 +7707,23 @@
           <t>Vassi GTX Pro Bib Men</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
         <v>2733284</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>898</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>1063812</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>326</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>3702955</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.253</v>
       </c>
     </row>
     <row r="44">
@@ -5275,23 +7742,23 @@
           <t>Astral GTX II Pant Men</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
         <v>-827</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>-1</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>2166969</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>1885</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>3697598</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.526</v>
       </c>
     </row>
     <row r="45">
@@ -5310,23 +7777,23 @@
           <t>Astral GTX Pant Men</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
         <v>2484339</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>2403</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>1530630</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>1699</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>3697598</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.474</v>
       </c>
     </row>
     <row r="46">
@@ -5345,23 +7812,23 @@
           <t>Puffy Mimic III Hood Men</t>
         </is>
       </c>
-      <c r="D46" t="n">
-        <v>0</v>
+      <c r="D46" t="b">
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
         <v>1531232</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>1716</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>3338363</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.476</v>
       </c>
     </row>
     <row r="47">
@@ -5380,23 +7847,23 @@
           <t>Puffy Mimic II HoodMen</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
         <v>47131</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>46</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>1558076</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>1664</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>3338363</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.461</v>
       </c>
     </row>
     <row r="48">
@@ -5415,23 +7882,23 @@
           <t>Puffy Mimic Hood Men</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
         <v>3009125</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>3201</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>249055</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>227</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>3338363</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.063</v>
       </c>
     </row>
     <row r="49">
@@ -5450,23 +7917,23 @@
           <t>Vassi GTX II Pant Men</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
         <v>7410</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>4</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>2045155</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>989</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>3159078</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.716</v>
       </c>
     </row>
     <row r="50">
@@ -5485,23 +7952,23 @@
           <t>Vassi GTX Pant Men</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
         <v>2633620</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>1085</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>1113923</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>393</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>3159078</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.284</v>
       </c>
     </row>
     <row r="51">
@@ -5520,23 +7987,23 @@
           <t>Chaos GTX II JacketMen</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
         <v>997</v>
       </c>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
       <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
         <v>2835745</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>2687</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>3136238</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.892</v>
       </c>
     </row>
     <row r="52">
@@ -5555,23 +8022,23 @@
           <t>Chaos GTX Jacket Men</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
         <v>3433953</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>3551</v>
       </c>
-      <c r="F52" t="n">
+      <c r="G52" t="n">
         <v>300493</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>325</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>3136238</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.108</v>
       </c>
     </row>
     <row r="53">
@@ -5590,23 +8057,23 @@
           <t>Haglöfs Ridge GTX Mid Women</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
         <v>1885514</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>2098</v>
       </c>
-      <c r="F53" t="n">
+      <c r="G53" t="n">
         <v>3066414</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>2827</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>3066414</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -5625,8 +8092,8 @@
           <t>Haglöfs Ridge GTX II Mid Women</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>0</v>
+      <c r="D54" t="b">
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -5638,10 +8105,10 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
         <v>3066414</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5660,23 +8127,23 @@
           <t>Chaos GTX II JacketWomen</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
         <v>997</v>
       </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
       <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
         <v>2223092</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>2124</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>2972960</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.671</v>
       </c>
     </row>
     <row r="56">
@@ -5695,23 +8162,23 @@
           <t>Chaos GTX Jacket Women</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
         <v>2475056</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>2536</v>
       </c>
-      <c r="F56" t="n">
+      <c r="G56" t="n">
         <v>749867</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>1043</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>2972960</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.329</v>
       </c>
     </row>
     <row r="57">
@@ -5730,23 +8197,23 @@
           <t>L.I.M Mimic Hood Men</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
         <v>2168640</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>1933</v>
       </c>
-      <c r="F57" t="n">
+      <c r="G57" t="n">
         <v>2158170</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>2457</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>2859992</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.778</v>
       </c>
     </row>
     <row r="58">
@@ -5765,23 +8232,23 @@
           <t>L.I.M Mimic II HoodMen</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
         <v>4726</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>5</v>
       </c>
-      <c r="F58" t="n">
+      <c r="G58" t="n">
         <v>701822</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>702</v>
       </c>
-      <c r="H58" t="n">
+      <c r="I58" t="n">
         <v>2859992</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.222</v>
       </c>
     </row>
     <row r="59">
@@ -5800,23 +8267,23 @@
           <t>Long Mimic III Parka Women</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>0</v>
+      <c r="D59" t="b">
+        <v>1</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
         <v>2553880</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>2261</v>
       </c>
-      <c r="H59" t="n">
+      <c r="I59" t="n">
         <v>2642404</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.9</v>
       </c>
     </row>
     <row r="60">
@@ -5835,23 +8302,23 @@
           <t>Long Mimic Parka Women</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
         <v>3571477</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>3369</v>
       </c>
-      <c r="F60" t="n">
+      <c r="G60" t="n">
         <v>925463</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>903</v>
       </c>
-      <c r="H60" t="n">
+      <c r="I60" t="n">
         <v>2642404</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.359</v>
       </c>
     </row>
     <row r="61">
@@ -5870,23 +8337,23 @@
           <t>Long Mimic II ParkaWomen</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
         <v>1121119</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>842</v>
       </c>
-      <c r="F61" t="n">
+      <c r="G61" t="n">
         <v>-836938</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>-651</v>
       </c>
-      <c r="H61" t="n">
+      <c r="I61" t="n">
         <v>2642404</v>
-      </c>
-      <c r="I61" t="n">
-        <v>-0.259</v>
       </c>
     </row>
     <row r="62">
@@ -5905,23 +8372,23 @@
           <t>L.I.M Down II Hood Men</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
         <v>4322</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>4</v>
       </c>
-      <c r="F62" t="n">
+      <c r="G62" t="n">
         <v>1295953</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>1193</v>
       </c>
-      <c r="H62" t="n">
+      <c r="I62" t="n">
         <v>2612863</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.539</v>
       </c>
     </row>
     <row r="63">
@@ -5940,23 +8407,23 @@
           <t>L.I.M Down Hood Men</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
         <v>1699811</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>1194</v>
       </c>
-      <c r="F63" t="n">
+      <c r="G63" t="n">
         <v>1316909</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>1020</v>
       </c>
-      <c r="H63" t="n">
+      <c r="I63" t="n">
         <v>2612863</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.461</v>
       </c>
     </row>
     <row r="64">
@@ -5975,23 +8442,23 @@
           <t>L.I.M Fuse II Pant Men</t>
         </is>
       </c>
-      <c r="D64" t="n">
-        <v>0</v>
+      <c r="D64" t="b">
+        <v>1</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
         <v>1236398</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>3544</v>
       </c>
-      <c r="H64" t="n">
+      <c r="I64" t="n">
         <v>2354324</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.547</v>
       </c>
     </row>
     <row r="65">
@@ -6010,23 +8477,23 @@
           <t>L.I.M Fuse Pant Men</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
         <v>1342745</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>3066</v>
       </c>
-      <c r="F65" t="n">
+      <c r="G65" t="n">
         <v>1117926</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>2934</v>
       </c>
-      <c r="H65" t="n">
+      <c r="I65" t="n">
         <v>2354324</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.453</v>
       </c>
     </row>
     <row r="66">
@@ -6045,23 +8512,23 @@
           <t>Vassi GTX II JacketWomen</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
         <v>5695</v>
       </c>
-      <c r="E66" t="n">
+      <c r="F66" t="n">
         <v>3</v>
       </c>
-      <c r="F66" t="n">
+      <c r="G66" t="n">
         <v>1270625</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>542</v>
       </c>
-      <c r="H66" t="n">
+      <c r="I66" t="n">
         <v>2312379</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.604</v>
       </c>
     </row>
     <row r="67">
@@ -6080,23 +8547,23 @@
           <t>Vassi GTX Jacket Women</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
         <v>1991265</v>
       </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>687</v>
       </c>
-      <c r="F67" t="n">
+      <c r="G67" t="n">
         <v>1041755</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>356</v>
       </c>
-      <c r="H67" t="n">
+      <c r="I67" t="n">
         <v>2312379</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.396</v>
       </c>
     </row>
     <row r="68">
@@ -6115,23 +8582,23 @@
           <t>Vassi GTX Pro II Jacket Women</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
         <v>5957</v>
       </c>
-      <c r="E68" t="n">
+      <c r="F68" t="n">
         <v>2</v>
       </c>
-      <c r="F68" t="n">
+      <c r="G68" t="n">
         <v>1216944</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>366</v>
       </c>
-      <c r="H68" t="n">
+      <c r="I68" t="n">
         <v>2128498</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0.574</v>
       </c>
     </row>
     <row r="69">
@@ -6150,23 +8617,23 @@
           <t>Vassi GTX Pro Jacket Women</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
         <v>1585753</v>
       </c>
-      <c r="E69" t="n">
+      <c r="F69" t="n">
         <v>458</v>
       </c>
-      <c r="F69" t="n">
+      <c r="G69" t="n">
         <v>911554</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>272</v>
       </c>
-      <c r="H69" t="n">
+      <c r="I69" t="n">
         <v>2128498</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.426</v>
       </c>
     </row>
     <row r="70">
@@ -6185,23 +8652,23 @@
           <t>L.I.M Fuse II Shorts Men</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>0</v>
+      <c r="D70" t="b">
+        <v>1</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
         <v>1308675</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>4272</v>
       </c>
-      <c r="H70" t="n">
+      <c r="I70" t="n">
         <v>2115481</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.594</v>
       </c>
     </row>
     <row r="71">
@@ -6220,23 +8687,23 @@
           <t>L.I.M Fuse Shorts Men</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
         <v>1742551</v>
       </c>
-      <c r="E71" t="n">
+      <c r="F71" t="n">
         <v>5487</v>
       </c>
-      <c r="F71" t="n">
+      <c r="G71" t="n">
         <v>806806</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>2916</v>
       </c>
-      <c r="H71" t="n">
+      <c r="I71" t="n">
         <v>2115481</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0.406</v>
       </c>
     </row>
     <row r="72">
@@ -6255,23 +8722,23 @@
           <t>L.I.M Fuse Pant Women</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
         <v>1619910</v>
       </c>
-      <c r="E72" t="n">
+      <c r="F72" t="n">
         <v>3451</v>
       </c>
-      <c r="F72" t="n">
+      <c r="G72" t="n">
         <v>1105882</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>2558</v>
       </c>
-      <c r="H72" t="n">
+      <c r="I72" t="n">
         <v>2023783</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.512</v>
       </c>
     </row>
     <row r="73">
@@ -6290,23 +8757,23 @@
           <t>L.I.M Fuse II Pant Women</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>0</v>
+      <c r="D73" t="b">
+        <v>1</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
         <v>917902</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>2437</v>
       </c>
-      <c r="H73" t="n">
+      <c r="I73" t="n">
         <v>2023783</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.488</v>
       </c>
     </row>
     <row r="74">
@@ -6325,23 +8792,23 @@
           <t>Vassi GTX Pro II Bib Women</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
         <v>2213</v>
       </c>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
       <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
         <v>1218578</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>446</v>
       </c>
-      <c r="H74" t="n">
+      <c r="I74" t="n">
         <v>2000243</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0.64</v>
       </c>
     </row>
     <row r="75">
@@ -6360,23 +8827,23 @@
           <t>Vassi GTX Pro Bib Women</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
         <v>1253997</v>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>409</v>
       </c>
-      <c r="F75" t="n">
+      <c r="G75" t="n">
         <v>781665</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>251</v>
       </c>
-      <c r="H75" t="n">
+      <c r="I75" t="n">
         <v>2000243</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0.36</v>
       </c>
     </row>
     <row r="76">
@@ -6395,23 +8862,23 @@
           <t>Salix Proof Mimic II Parka Women</t>
         </is>
       </c>
-      <c r="D76" t="n">
-        <v>0</v>
+      <c r="D76" t="b">
+        <v>1</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
         <v>1456929</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>1394</v>
       </c>
-      <c r="H76" t="n">
+      <c r="I76" t="n">
         <v>1969208</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.758</v>
       </c>
     </row>
     <row r="77">
@@ -6430,23 +8897,23 @@
           <t>Salix Proof Mimic Parka Women</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
         <v>2538892</v>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>2173</v>
       </c>
-      <c r="F77" t="n">
+      <c r="G77" t="n">
         <v>512279</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>445</v>
       </c>
-      <c r="H77" t="n">
+      <c r="I77" t="n">
         <v>1969208</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0.242</v>
       </c>
     </row>
     <row r="78">
@@ -6465,23 +8932,23 @@
           <t>Bield Down II Hood Women</t>
         </is>
       </c>
-      <c r="D78" t="n">
-        <v>0</v>
+      <c r="D78" t="b">
+        <v>1</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
         <v>1627659</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>1952</v>
       </c>
-      <c r="H78" t="n">
+      <c r="I78" t="n">
         <v>1940455</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0.844</v>
       </c>
     </row>
     <row r="79">
@@ -6500,23 +8967,23 @@
           <t>Bield Down Hood Women</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
         <v>2945652</v>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>3480</v>
       </c>
-      <c r="F79" t="n">
+      <c r="G79" t="n">
         <v>312795</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>361</v>
       </c>
-      <c r="H79" t="n">
+      <c r="I79" t="n">
         <v>1940455</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0.156</v>
       </c>
     </row>
     <row r="80">
@@ -6535,23 +9002,23 @@
           <t>L.I.M Mimic Hood Women</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
         <v>1530640</v>
       </c>
-      <c r="E80" t="n">
+      <c r="F80" t="n">
         <v>1384</v>
       </c>
-      <c r="F80" t="n">
+      <c r="G80" t="n">
         <v>1348064</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>1421</v>
       </c>
-      <c r="H80" t="n">
+      <c r="I80" t="n">
         <v>1825958</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.74</v>
       </c>
     </row>
     <row r="81">
@@ -6570,23 +9037,23 @@
           <t>L.I.M Mimic II HoodWomen</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
         <v>6652</v>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>7</v>
       </c>
-      <c r="F81" t="n">
+      <c r="G81" t="n">
         <v>477894</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>499</v>
       </c>
-      <c r="H81" t="n">
+      <c r="I81" t="n">
         <v>1825958</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0.26</v>
       </c>
     </row>
     <row r="82">
@@ -6605,23 +9072,23 @@
           <t>Vassi GTX II Pant Women</t>
         </is>
       </c>
-      <c r="D82" t="n">
-        <v>0</v>
+      <c r="D82" t="b">
+        <v>1</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
         <v>1033627</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>504</v>
       </c>
-      <c r="H82" t="n">
+      <c r="I82" t="n">
         <v>1661586</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.671</v>
       </c>
     </row>
     <row r="83">
@@ -6640,23 +9107,23 @@
           <t>Vassi GTX Pant Women</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" t="b">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
         <v>1280215</v>
       </c>
-      <c r="E83" t="n">
+      <c r="F83" t="n">
         <v>514</v>
       </c>
-      <c r="F83" t="n">
+      <c r="G83" t="n">
         <v>627959</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>247</v>
       </c>
-      <c r="H83" t="n">
+      <c r="I83" t="n">
         <v>1661586</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0.329</v>
       </c>
     </row>
     <row r="84">
@@ -6675,23 +9142,23 @@
           <t>L.I.M Fuse II Shorts Women</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>0</v>
+      <c r="D84" t="b">
+        <v>1</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
         <v>1076786</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>3091</v>
       </c>
-      <c r="H84" t="n">
+      <c r="I84" t="n">
         <v>1646528</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.609</v>
       </c>
     </row>
     <row r="85">
@@ -6710,23 +9177,23 @@
           <t>L.I.M Fuse Shorts Women</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" t="b">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
         <v>1227230</v>
       </c>
-      <c r="E85" t="n">
+      <c r="F85" t="n">
         <v>3773</v>
       </c>
-      <c r="F85" t="n">
+      <c r="G85" t="n">
         <v>569742</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>1986</v>
       </c>
-      <c r="H85" t="n">
+      <c r="I85" t="n">
         <v>1646528</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0.391</v>
       </c>
     </row>
     <row r="86">
@@ -6745,23 +9212,23 @@
           <t>L.I.M Alpha Hood Men</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" t="b">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
         <v>760918</v>
       </c>
-      <c r="E86" t="n">
+      <c r="F86" t="n">
         <v>545</v>
       </c>
-      <c r="F86" t="n">
+      <c r="G86" t="n">
         <v>1271961</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>1293</v>
       </c>
-      <c r="H86" t="n">
+      <c r="I86" t="n">
         <v>1641642</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0.741</v>
       </c>
     </row>
     <row r="87">
@@ -6780,23 +9247,23 @@
           <t>L.I.M Alpha II HoodMen</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v>0</v>
+      <c r="D87" t="b">
+        <v>1</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
         <v>369680</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>452</v>
       </c>
-      <c r="H87" t="n">
+      <c r="I87" t="n">
         <v>1641642</v>
-      </c>
-      <c r="I87" t="n">
-        <v>0.259</v>
       </c>
     </row>
     <row r="88">
@@ -6815,23 +9282,23 @@
           <t>L.I.M Mid Multi II Hood Men</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" t="n">
         <v>391</v>
       </c>
-      <c r="E88" t="n">
-        <v>1</v>
-      </c>
       <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
         <v>1167774</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>2355</v>
       </c>
-      <c r="H88" t="n">
+      <c r="I88" t="n">
         <v>1639814</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0.717</v>
       </c>
     </row>
     <row r="89">
@@ -6850,23 +9317,23 @@
           <t>L.I.M Mid Multi Hood Men</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" t="b">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
         <v>1275471</v>
       </c>
-      <c r="E89" t="n">
+      <c r="F89" t="n">
         <v>2668</v>
       </c>
-      <c r="F89" t="n">
+      <c r="G89" t="n">
         <v>472040</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>931</v>
       </c>
-      <c r="H89" t="n">
+      <c r="I89" t="n">
         <v>1639814</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0.283</v>
       </c>
     </row>
     <row r="90">
@@ -6885,23 +9352,23 @@
           <t>L.I.M Down Hood Women</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" t="b">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
         <v>1385802</v>
       </c>
-      <c r="E90" t="n">
+      <c r="F90" t="n">
         <v>1078</v>
       </c>
-      <c r="F90" t="n">
+      <c r="G90" t="n">
         <v>869409</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>808</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
         <v>1487577</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0.552</v>
       </c>
     </row>
     <row r="91">
@@ -6920,23 +9387,23 @@
           <t>L.I.M Down II Hood Women</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
         <v>4322</v>
       </c>
-      <c r="E91" t="n">
+      <c r="F91" t="n">
         <v>4</v>
       </c>
-      <c r="F91" t="n">
+      <c r="G91" t="n">
         <v>618168</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>656</v>
       </c>
-      <c r="H91" t="n">
+      <c r="I91" t="n">
         <v>1487577</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0.448</v>
       </c>
     </row>
     <row r="92">
@@ -6955,23 +9422,23 @@
           <t>L.I.M Down Jacket Men</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
         <v>978714</v>
       </c>
-      <c r="E92" t="n">
+      <c r="F92" t="n">
         <v>731</v>
       </c>
-      <c r="F92" t="n">
+      <c r="G92" t="n">
         <v>926599</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>812</v>
       </c>
-      <c r="H92" t="n">
+      <c r="I92" t="n">
         <v>1467016</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0.572</v>
       </c>
     </row>
     <row r="93">
@@ -6990,23 +9457,23 @@
           <t>L.I.M Down II Jacket Men</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" t="n">
         <v>2835</v>
       </c>
-      <c r="E93" t="n">
+      <c r="F93" t="n">
         <v>3</v>
       </c>
-      <c r="F93" t="n">
+      <c r="G93" t="n">
         <v>540417</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>608</v>
       </c>
-      <c r="H93" t="n">
+      <c r="I93" t="n">
         <v>1467016</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0.428</v>
       </c>
     </row>
     <row r="94">
@@ -7025,23 +9492,23 @@
           <t>Riksgränsen Down 850 II Hood Men</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
         <v>3948</v>
       </c>
-      <c r="E94" t="n">
+      <c r="F94" t="n">
         <v>2</v>
       </c>
-      <c r="F94" t="n">
+      <c r="G94" t="n">
         <v>910695</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>414</v>
       </c>
-      <c r="H94" t="n">
+      <c r="I94" t="n">
         <v>1444637</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0.68</v>
       </c>
     </row>
     <row r="95">
@@ -7060,23 +9527,23 @@
           <t>Riksgränsen Down 850 Hood Men</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" t="b">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
         <v>1503152</v>
       </c>
-      <c r="E95" t="n">
+      <c r="F95" t="n">
         <v>533</v>
       </c>
-      <c r="F95" t="n">
+      <c r="G95" t="n">
         <v>533942</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>195</v>
       </c>
-      <c r="H95" t="n">
+      <c r="I95" t="n">
         <v>1444637</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0.32</v>
       </c>
     </row>
     <row r="96">
@@ -7095,23 +9562,23 @@
           <t>L.I.M Mid Multi II Hood Women</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" t="n">
         <v>391</v>
       </c>
-      <c r="E96" t="n">
-        <v>1</v>
-      </c>
       <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
         <v>881849</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>1670</v>
       </c>
-      <c r="H96" t="n">
+      <c r="I96" t="n">
         <v>1286163</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0.639</v>
       </c>
     </row>
     <row r="97">
@@ -7130,23 +9597,23 @@
           <t>L.I.M Mid Multi Hood Women</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" t="b">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
         <v>964026</v>
       </c>
-      <c r="E97" t="n">
+      <c r="F97" t="n">
         <v>1934</v>
       </c>
-      <c r="F97" t="n">
+      <c r="G97" t="n">
         <v>404315</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>942</v>
       </c>
-      <c r="H97" t="n">
+      <c r="I97" t="n">
         <v>1286163</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0.361</v>
       </c>
     </row>
     <row r="98">
@@ -7165,23 +9632,23 @@
           <t>Bow Windstopper Glove</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" t="b">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
         <v>468264</v>
       </c>
-      <c r="E98" t="n">
+      <c r="F98" t="n">
         <v>1269</v>
       </c>
-      <c r="F98" t="n">
+      <c r="G98" t="n">
         <v>956326</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>5238</v>
       </c>
-      <c r="H98" t="n">
+      <c r="I98" t="n">
         <v>1225569</v>
-      </c>
-      <c r="I98" t="n">
-        <v>0.859</v>
       </c>
     </row>
     <row r="99">
@@ -7200,23 +9667,23 @@
           <t>Bow Windstopper II Glove</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
         <v>1047</v>
       </c>
-      <c r="E99" t="n">
+      <c r="F99" t="n">
         <v>4</v>
       </c>
-      <c r="F99" t="n">
+      <c r="G99" t="n">
         <v>269243</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>863</v>
       </c>
-      <c r="H99" t="n">
+      <c r="I99" t="n">
         <v>1225569</v>
-      </c>
-      <c r="I99" t="n">
-        <v>0.141</v>
       </c>
     </row>
     <row r="100">
@@ -7235,23 +9702,23 @@
           <t>Korp Proof Pant Men</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" t="b">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
         <v>443876</v>
       </c>
-      <c r="E100" t="n">
+      <c r="F100" t="n">
         <v>817</v>
       </c>
-      <c r="F100" t="n">
+      <c r="G100" t="n">
         <v>733412</v>
       </c>
-      <c r="G100" t="n">
+      <c r="H100" t="n">
         <v>1468</v>
       </c>
-      <c r="H100" t="n">
+      <c r="I100" t="n">
         <v>1210200</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0.55</v>
       </c>
     </row>
     <row r="101">
@@ -7270,23 +9737,23 @@
           <t>Korp Proof II Pant Men</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>0</v>
+      <c r="D101" t="b">
+        <v>1</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
         <v>476787</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>1199</v>
       </c>
-      <c r="H101" t="n">
+      <c r="I101" t="n">
         <v>1210200</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0.45</v>
       </c>
     </row>
     <row r="102">
@@ -7305,23 +9772,23 @@
           <t>Lite Standard Zip-Off Pant Men</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
         <v>929142</v>
       </c>
-      <c r="E102" t="n">
+      <c r="F102" t="n">
         <v>1612</v>
       </c>
-      <c r="F102" t="n">
+      <c r="G102" t="n">
         <v>1107833</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>1991</v>
       </c>
-      <c r="H102" t="n">
+      <c r="I102" t="n">
         <v>1204947</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0.826</v>
       </c>
     </row>
     <row r="103">
@@ -7340,23 +9807,23 @@
           <t>Lite Standard Zip-Off II Pant Men</t>
         </is>
       </c>
-      <c r="D103" t="n">
-        <v>0</v>
+      <c r="D103" t="b">
+        <v>1</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
       </c>
       <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
         <v>97114</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>420</v>
       </c>
-      <c r="H103" t="n">
+      <c r="I103" t="n">
         <v>1204947</v>
-      </c>
-      <c r="I103" t="n">
-        <v>0.174</v>
       </c>
     </row>
     <row r="104">
@@ -7375,23 +9842,23 @@
           <t>Gran 3-in-1 Proof II Jacket Men</t>
         </is>
       </c>
-      <c r="D104" t="n">
-        <v>0</v>
+      <c r="D104" t="b">
+        <v>1</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
         <v>976727</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>1083</v>
       </c>
-      <c r="H104" t="n">
+      <c r="I104" t="n">
         <v>1190578</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0.86</v>
       </c>
     </row>
     <row r="105">
@@ -7410,23 +9877,23 @@
           <t>Gran 3-in-1 Proof Jacket Men</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" t="b">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
         <v>859312</v>
       </c>
-      <c r="E105" t="n">
+      <c r="F105" t="n">
         <v>879</v>
       </c>
-      <c r="F105" t="n">
+      <c r="G105" t="n">
         <v>213850</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>177</v>
       </c>
-      <c r="H105" t="n">
+      <c r="I105" t="n">
         <v>1190578</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0.14</v>
       </c>
     </row>
     <row r="106">
@@ -7445,23 +9912,23 @@
           <t>L.I.M Mid Fast II Hood Men</t>
         </is>
       </c>
-      <c r="D106" t="n">
-        <v>0</v>
+      <c r="D106" t="b">
+        <v>1</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
         <v>654238</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>968</v>
       </c>
-      <c r="H106" t="n">
+      <c r="I106" t="n">
         <v>1187878</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0.526</v>
       </c>
     </row>
     <row r="107">
@@ -7480,23 +9947,23 @@
           <t>L.I.M Mid Fast HoodMen</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" t="b">
+        <v>0</v>
+      </c>
+      <c r="E107" t="n">
         <v>582030</v>
       </c>
-      <c r="E107" t="n">
+      <c r="F107" t="n">
         <v>862</v>
       </c>
-      <c r="F107" t="n">
+      <c r="G107" t="n">
         <v>533639</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>874</v>
       </c>
-      <c r="H107" t="n">
+      <c r="I107" t="n">
         <v>1187878</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0.474</v>
       </c>
     </row>
     <row r="108">
@@ -7515,23 +9982,23 @@
           <t>Haglöfs Krusa GTX Low Women</t>
         </is>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" t="b">
+        <v>0</v>
+      </c>
+      <c r="E108" t="n">
         <v>543697</v>
       </c>
-      <c r="E108" t="n">
+      <c r="F108" t="n">
         <v>863</v>
       </c>
-      <c r="F108" t="n">
+      <c r="G108" t="n">
         <v>1175486</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>1906</v>
       </c>
-      <c r="H108" t="n">
+      <c r="I108" t="n">
         <v>1175486</v>
-      </c>
-      <c r="I108" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -7550,8 +10017,8 @@
           <t>Haglöfs Krusa GTX II Low Women</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>0</v>
+      <c r="D109" t="b">
+        <v>1</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -7563,10 +10030,10 @@
         <v>0</v>
       </c>
       <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
         <v>1175486</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -7585,23 +10052,23 @@
           <t>Chaos GTX II Pant Women</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>0</v>
+      <c r="D110" t="b">
+        <v>1</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
       </c>
       <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
         <v>916462</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>1057</v>
       </c>
-      <c r="H110" t="n">
+      <c r="I110" t="n">
         <v>1152280</v>
-      </c>
-      <c r="I110" t="n">
-        <v>0.795</v>
       </c>
     </row>
     <row r="111">
@@ -7620,23 +10087,23 @@
           <t>Chaos GTX Pant Women</t>
         </is>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" t="b">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
         <v>1502874</v>
       </c>
-      <c r="E111" t="n">
+      <c r="F111" t="n">
         <v>1757</v>
       </c>
-      <c r="F111" t="n">
+      <c r="G111" t="n">
         <v>235818</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>272</v>
       </c>
-      <c r="H111" t="n">
+      <c r="I111" t="n">
         <v>1152280</v>
-      </c>
-      <c r="I111" t="n">
-        <v>0.205</v>
       </c>
     </row>
     <row r="112">
@@ -7655,23 +10122,23 @@
           <t>Chaos GTX II Pant Men</t>
         </is>
       </c>
-      <c r="D112" t="n">
-        <v>0</v>
+      <c r="D112" t="b">
+        <v>1</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
       </c>
       <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
         <v>912538</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>1062</v>
       </c>
-      <c r="H112" t="n">
+      <c r="I112" t="n">
         <v>1086368</v>
-      </c>
-      <c r="I112" t="n">
-        <v>0.859</v>
       </c>
     </row>
     <row r="113">
@@ -7690,23 +10157,23 @@
           <t>Chaos GTX Pant Men</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" t="b">
+        <v>0</v>
+      </c>
+      <c r="E113" t="n">
         <v>1181308</v>
       </c>
-      <c r="E113" t="n">
+      <c r="F113" t="n">
         <v>1365</v>
       </c>
-      <c r="F113" t="n">
+      <c r="G113" t="n">
         <v>173830</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>174</v>
       </c>
-      <c r="H113" t="n">
+      <c r="I113" t="n">
         <v>1086368</v>
-      </c>
-      <c r="I113" t="n">
-        <v>0.141</v>
       </c>
     </row>
     <row r="114">
@@ -7725,23 +10192,23 @@
           <t>Korp Proof Pant Women</t>
         </is>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" t="b">
+        <v>0</v>
+      </c>
+      <c r="E114" t="n">
         <v>542309</v>
       </c>
-      <c r="E114" t="n">
+      <c r="F114" t="n">
         <v>1034</v>
       </c>
-      <c r="F114" t="n">
+      <c r="G114" t="n">
         <v>642781</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>1384</v>
       </c>
-      <c r="H114" t="n">
+      <c r="I114" t="n">
         <v>1078722</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0.587</v>
       </c>
     </row>
     <row r="115">
@@ -7760,23 +10227,23 @@
           <t>Korp Proof II Pant Women</t>
         </is>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" t="b">
+        <v>1</v>
+      </c>
+      <c r="E115" t="n">
         <v>-619</v>
       </c>
-      <c r="E115" t="n">
+      <c r="F115" t="n">
         <v>-1</v>
       </c>
-      <c r="F115" t="n">
+      <c r="G115" t="n">
         <v>435941</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>973</v>
       </c>
-      <c r="H115" t="n">
+      <c r="I115" t="n">
         <v>1078722</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0.413</v>
       </c>
     </row>
     <row r="116">
@@ -7795,23 +10262,23 @@
           <t>Lite Standard Zip-Off Pant Women</t>
         </is>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" t="b">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
         <v>1185164</v>
       </c>
-      <c r="E116" t="n">
+      <c r="F116" t="n">
         <v>2179</v>
       </c>
-      <c r="F116" t="n">
+      <c r="G116" t="n">
         <v>1018734</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>1874</v>
       </c>
-      <c r="H116" t="n">
+      <c r="I116" t="n">
         <v>1018734</v>
-      </c>
-      <c r="I116" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -7830,8 +10297,8 @@
           <t>Lite Standard Zip-Off II Pant Women</t>
         </is>
       </c>
-      <c r="D117" t="n">
-        <v>0</v>
+      <c r="D117" t="b">
+        <v>1</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -7843,10 +10310,10 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
         <v>1018734</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -7865,23 +10332,23 @@
           <t>Vandra Pant Women</t>
         </is>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" t="b">
+        <v>0</v>
+      </c>
+      <c r="E118" t="n">
         <v>2245206</v>
       </c>
-      <c r="E118" t="n">
+      <c r="F118" t="n">
         <v>3133</v>
       </c>
-      <c r="F118" t="n">
+      <c r="G118" t="n">
         <v>964308</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>1002</v>
       </c>
-      <c r="H118" t="n">
+      <c r="I118" t="n">
         <v>964308</v>
-      </c>
-      <c r="I118" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -7900,23 +10367,23 @@
           <t>Vandra II Pant Women</t>
         </is>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" t="b">
+        <v>1</v>
+      </c>
+      <c r="E119" t="n">
         <v>-1026</v>
       </c>
-      <c r="E119" t="n">
+      <c r="F119" t="n">
         <v>-1</v>
       </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
         <v>964308</v>
-      </c>
-      <c r="I119" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -7935,23 +10402,23 @@
           <t>L.I.M Mid Fast HoodWomen</t>
         </is>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" t="b">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
         <v>433205</v>
       </c>
-      <c r="E120" t="n">
+      <c r="F120" t="n">
         <v>630</v>
       </c>
-      <c r="F120" t="n">
+      <c r="G120" t="n">
         <v>513876</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>869</v>
       </c>
-      <c r="H120" t="n">
+      <c r="I120" t="n">
         <v>893342</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0.609</v>
       </c>
     </row>
     <row r="121">
@@ -7970,23 +10437,23 @@
           <t>L.I.M Mid Fast II Hood Women</t>
         </is>
       </c>
-      <c r="D121" t="n">
-        <v>0</v>
+      <c r="D121" t="b">
+        <v>1</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
       </c>
       <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
         <v>379465</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>559</v>
       </c>
-      <c r="H121" t="n">
+      <c r="I121" t="n">
         <v>893342</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0.391</v>
       </c>
     </row>
     <row r="122">
@@ -8005,23 +10472,23 @@
           <t>Fiction Down II Hood Men</t>
         </is>
       </c>
-      <c r="D122" t="n">
-        <v>0</v>
+      <c r="D122" t="b">
+        <v>1</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
       </c>
       <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
         <v>813427</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>918</v>
       </c>
-      <c r="H122" t="n">
+      <c r="I122" t="n">
         <v>872697</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0.955</v>
       </c>
     </row>
     <row r="123">
@@ -8040,23 +10507,23 @@
           <t>Fiction Down Hood Men</t>
         </is>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" t="b">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
         <v>1334146</v>
       </c>
-      <c r="E123" t="n">
+      <c r="F123" t="n">
         <v>1446</v>
       </c>
-      <c r="F123" t="n">
+      <c r="G123" t="n">
         <v>59270</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>43</v>
       </c>
-      <c r="H123" t="n">
+      <c r="I123" t="n">
         <v>872697</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0.045</v>
       </c>
     </row>
     <row r="124">
@@ -8075,23 +10542,23 @@
           <t>Base Mimic II Hood Men</t>
         </is>
       </c>
-      <c r="D124" t="n">
-        <v>0</v>
+      <c r="D124" t="b">
+        <v>1</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
       <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
         <v>855190</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>1091</v>
       </c>
-      <c r="H124" t="n">
+      <c r="I124" t="n">
         <v>855190</v>
-      </c>
-      <c r="I124" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="125">
@@ -8110,23 +10577,23 @@
           <t>Base Mimic Hood Men</t>
         </is>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" t="b">
+        <v>0</v>
+      </c>
+      <c r="E125" t="n">
         <v>31962</v>
       </c>
-      <c r="E125" t="n">
+      <c r="F125" t="n">
         <v>35</v>
       </c>
-      <c r="F125" t="n">
-        <v>0</v>
-      </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
         <v>855190</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -8145,23 +10612,23 @@
           <t>Mountain II Cap</t>
         </is>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" t="b">
+        <v>1</v>
+      </c>
+      <c r="E126" t="n">
         <v>2169</v>
       </c>
-      <c r="E126" t="n">
+      <c r="F126" t="n">
         <v>11</v>
       </c>
-      <c r="F126" t="n">
+      <c r="G126" t="n">
         <v>745523</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>3460</v>
       </c>
-      <c r="H126" t="n">
+      <c r="I126" t="n">
         <v>848782</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0.855</v>
       </c>
     </row>
     <row r="127">
@@ -8180,23 +10647,23 @@
           <t>Mountain Cap</t>
         </is>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" t="b">
+        <v>0</v>
+      </c>
+      <c r="E127" t="n">
         <v>212119</v>
       </c>
-      <c r="E127" t="n">
+      <c r="F127" t="n">
         <v>777</v>
       </c>
-      <c r="F127" t="n">
+      <c r="G127" t="n">
         <v>103259</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>589</v>
       </c>
-      <c r="H127" t="n">
+      <c r="I127" t="n">
         <v>848782</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0.145</v>
       </c>
     </row>
     <row r="128">
@@ -8215,23 +10682,23 @@
           <t>Riksgränsen Down 850 II Hood Women</t>
         </is>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" t="b">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
         <v>1955</v>
       </c>
-      <c r="E128" t="n">
-        <v>1</v>
-      </c>
       <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="n">
         <v>434759</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>206</v>
       </c>
-      <c r="H128" t="n">
+      <c r="I128" t="n">
         <v>833149</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0.571</v>
       </c>
     </row>
     <row r="129">
@@ -8250,23 +10717,23 @@
           <t>Riksgränsen Down 850 Hood Women</t>
         </is>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" t="b">
+        <v>0</v>
+      </c>
+      <c r="E129" t="n">
         <v>536413</v>
       </c>
-      <c r="E129" t="n">
+      <c r="F129" t="n">
         <v>189</v>
       </c>
-      <c r="F129" t="n">
+      <c r="G129" t="n">
         <v>398390</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>155</v>
       </c>
-      <c r="H129" t="n">
+      <c r="I129" t="n">
         <v>833149</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0.429</v>
       </c>
     </row>
     <row r="130">
@@ -8285,23 +10752,23 @@
           <t>Puffy Mimic II HoodWomen</t>
         </is>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" t="b">
+        <v>1</v>
+      </c>
+      <c r="E130" t="n">
         <v>34209</v>
       </c>
-      <c r="E130" t="n">
+      <c r="F130" t="n">
         <v>33</v>
       </c>
-      <c r="F130" t="n">
+      <c r="G130" t="n">
         <v>546244</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>663</v>
       </c>
-      <c r="H130" t="n">
+      <c r="I130" t="n">
         <v>824788</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -8320,23 +10787,23 @@
           <t>Puffy Mimic Hood Women</t>
         </is>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" t="b">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
         <v>916300</v>
       </c>
-      <c r="E131" t="n">
+      <c r="F131" t="n">
         <v>1045</v>
       </c>
-      <c r="F131" t="n">
+      <c r="G131" t="n">
         <v>278545</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>306</v>
       </c>
-      <c r="H131" t="n">
+      <c r="I131" t="n">
         <v>824788</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0.316</v>
       </c>
     </row>
     <row r="132">
@@ -8355,23 +10822,23 @@
           <t>L.I.M Alpha Hood Women</t>
         </is>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" t="b">
+        <v>0</v>
+      </c>
+      <c r="E132" t="n">
         <v>350600</v>
       </c>
-      <c r="E132" t="n">
+      <c r="F132" t="n">
         <v>280</v>
       </c>
-      <c r="F132" t="n">
+      <c r="G132" t="n">
         <v>677197</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>700</v>
       </c>
-      <c r="H132" t="n">
+      <c r="I132" t="n">
         <v>819747</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0.782</v>
       </c>
     </row>
     <row r="133">
@@ -8390,23 +10857,23 @@
           <t>L.I.M Alpha II HoodWomen</t>
         </is>
       </c>
-      <c r="D133" t="n">
-        <v>0</v>
+      <c r="D133" t="b">
+        <v>1</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
       </c>
       <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
         <v>142550</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>195</v>
       </c>
-      <c r="H133" t="n">
+      <c r="I133" t="n">
         <v>819747</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0.218</v>
       </c>
     </row>
     <row r="134">
@@ -8425,23 +10892,23 @@
           <t>Essens Down II HoodWomen</t>
         </is>
       </c>
-      <c r="D134" t="n">
-        <v>0</v>
+      <c r="D134" t="b">
+        <v>1</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
       </c>
       <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
         <v>816725</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>1008</v>
       </c>
-      <c r="H134" t="n">
+      <c r="I134" t="n">
         <v>817618</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0.997</v>
       </c>
     </row>
     <row r="135">
@@ -8460,23 +10927,23 @@
           <t>Essens Down Hood Women</t>
         </is>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" t="b">
+        <v>0</v>
+      </c>
+      <c r="E135" t="n">
         <v>2593</v>
       </c>
-      <c r="E135" t="n">
+      <c r="F135" t="n">
         <v>2</v>
       </c>
-      <c r="F135" t="n">
+      <c r="G135" t="n">
         <v>893</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>3</v>
       </c>
-      <c r="H135" t="n">
+      <c r="I135" t="n">
         <v>817618</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0.003</v>
       </c>
     </row>
     <row r="136">
@@ -8495,23 +10962,23 @@
           <t>Base Mimic II Hood Women</t>
         </is>
       </c>
-      <c r="D136" t="n">
-        <v>0</v>
+      <c r="D136" t="b">
+        <v>1</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
       </c>
       <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
         <v>791678</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>1010</v>
       </c>
-      <c r="H136" t="n">
+      <c r="I136" t="n">
         <v>791678</v>
-      </c>
-      <c r="I136" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -8530,23 +10997,23 @@
           <t>Base Mimic Hood Women</t>
         </is>
       </c>
-      <c r="D137" t="n">
+      <c r="D137" t="b">
+        <v>0</v>
+      </c>
+      <c r="E137" t="n">
         <v>94693</v>
       </c>
-      <c r="E137" t="n">
+      <c r="F137" t="n">
         <v>102</v>
       </c>
-      <c r="F137" t="n">
-        <v>0</v>
-      </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
         <v>791678</v>
-      </c>
-      <c r="I137" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -8565,23 +11032,23 @@
           <t>Zircon Shorts Men</t>
         </is>
       </c>
-      <c r="D138" t="n">
+      <c r="D138" t="b">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
         <v>2373757</v>
       </c>
-      <c r="E138" t="n">
+      <c r="F138" t="n">
         <v>5311</v>
       </c>
-      <c r="F138" t="n">
+      <c r="G138" t="n">
         <v>687615</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>1388</v>
       </c>
-      <c r="H138" t="n">
+      <c r="I138" t="n">
         <v>712247</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0.975</v>
       </c>
     </row>
     <row r="139">
@@ -8600,23 +11067,23 @@
           <t>Zircon 2.0 Shorts Men</t>
         </is>
       </c>
-      <c r="D139" t="n">
+      <c r="D139" t="b">
+        <v>1</v>
+      </c>
+      <c r="E139" t="n">
         <v>223247</v>
       </c>
-      <c r="E139" t="n">
+      <c r="F139" t="n">
         <v>468</v>
       </c>
-      <c r="F139" t="n">
+      <c r="G139" t="n">
         <v>24632</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>35</v>
       </c>
-      <c r="H139" t="n">
+      <c r="I139" t="n">
         <v>712247</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0.025</v>
       </c>
     </row>
     <row r="140">
@@ -8635,23 +11102,23 @@
           <t>L.I.M Mimic Vest Men</t>
         </is>
       </c>
-      <c r="D140" t="n">
+      <c r="D140" t="b">
+        <v>0</v>
+      </c>
+      <c r="E140" t="n">
         <v>253085</v>
       </c>
-      <c r="E140" t="n">
+      <c r="F140" t="n">
         <v>302</v>
       </c>
-      <c r="F140" t="n">
+      <c r="G140" t="n">
         <v>682249</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>1097</v>
       </c>
-      <c r="H140" t="n">
+      <c r="I140" t="n">
         <v>682770</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0.999</v>
       </c>
     </row>
     <row r="141">
@@ -8670,23 +11137,23 @@
           <t>L.I.M Mimic II VestMen</t>
         </is>
       </c>
-      <c r="D141" t="n">
-        <v>0</v>
+      <c r="D141" t="b">
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
       </c>
       <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
         <v>521</v>
       </c>
-      <c r="G141" t="n">
-        <v>1</v>
-      </c>
       <c r="H141" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" t="n">
         <v>682770</v>
-      </c>
-      <c r="I141" t="n">
-        <v>0.001</v>
       </c>
     </row>
     <row r="142">
@@ -8705,23 +11172,23 @@
           <t>L.I.M Critus II Pant Men</t>
         </is>
       </c>
-      <c r="D142" t="n">
-        <v>0</v>
+      <c r="D142" t="b">
+        <v>1</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
       </c>
       <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
         <v>633946</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>1039</v>
       </c>
-      <c r="H142" t="n">
+      <c r="I142" t="n">
         <v>653770</v>
-      </c>
-      <c r="I142" t="n">
-        <v>0.98</v>
       </c>
     </row>
     <row r="143">
@@ -8740,23 +11207,23 @@
           <t>L.I.M Critus Pant Men</t>
         </is>
       </c>
-      <c r="D143" t="n">
+      <c r="D143" t="b">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
         <v>1869025</v>
       </c>
-      <c r="E143" t="n">
+      <c r="F143" t="n">
         <v>3206</v>
       </c>
-      <c r="F143" t="n">
+      <c r="G143" t="n">
         <v>19824</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>21</v>
       </c>
-      <c r="H143" t="n">
+      <c r="I143" t="n">
         <v>653770</v>
-      </c>
-      <c r="I143" t="n">
-        <v>0.02</v>
       </c>
     </row>
     <row r="144">
@@ -8775,23 +11242,23 @@
           <t>Mila II Jacket Men</t>
         </is>
       </c>
-      <c r="D144" t="n">
-        <v>0</v>
+      <c r="D144" t="b">
+        <v>1</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
       </c>
       <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
         <v>638616</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>956</v>
       </c>
-      <c r="H144" t="n">
+      <c r="I144" t="n">
         <v>635314</v>
-      </c>
-      <c r="I144" t="n">
-        <v>1.002</v>
       </c>
     </row>
     <row r="145">
@@ -8810,23 +11277,23 @@
           <t>Mila Jacket Men</t>
         </is>
       </c>
-      <c r="D145" t="n">
+      <c r="D145" t="b">
+        <v>0</v>
+      </c>
+      <c r="E145" t="n">
         <v>545213</v>
       </c>
-      <c r="E145" t="n">
+      <c r="F145" t="n">
         <v>786</v>
       </c>
-      <c r="F145" t="n">
+      <c r="G145" t="n">
         <v>-3302</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>-2</v>
       </c>
-      <c r="H145" t="n">
+      <c r="I145" t="n">
         <v>635314</v>
-      </c>
-      <c r="I145" t="n">
-        <v>-0.002</v>
       </c>
     </row>
     <row r="146">
@@ -8845,23 +11312,23 @@
           <t>Zircon Shorts Women</t>
         </is>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" t="b">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
         <v>2087816</v>
       </c>
-      <c r="E146" t="n">
+      <c r="F146" t="n">
         <v>4674</v>
       </c>
-      <c r="F146" t="n">
+      <c r="G146" t="n">
         <v>610199</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>1225</v>
       </c>
-      <c r="H146" t="n">
+      <c r="I146" t="n">
         <v>610199</v>
-      </c>
-      <c r="I146" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -8880,23 +11347,23 @@
           <t>Zircon 2.0 Shorts Women</t>
         </is>
       </c>
-      <c r="D147" t="n">
+      <c r="D147" t="b">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
         <v>256800</v>
       </c>
-      <c r="E147" t="n">
+      <c r="F147" t="n">
         <v>600</v>
       </c>
-      <c r="F147" t="n">
-        <v>0</v>
-      </c>
       <c r="G147" t="n">
         <v>0</v>
       </c>
       <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
         <v>610199</v>
-      </c>
-      <c r="I147" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -8915,23 +11382,23 @@
           <t>L.I.M Critus II Pant Women</t>
         </is>
       </c>
-      <c r="D148" t="n">
-        <v>0</v>
+      <c r="D148" t="b">
+        <v>1</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
       </c>
       <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
         <v>609331</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>999</v>
       </c>
-      <c r="H148" t="n">
+      <c r="I148" t="n">
         <v>609331</v>
-      </c>
-      <c r="I148" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -8950,23 +11417,23 @@
           <t>L.I.M Critus Pant Women</t>
         </is>
       </c>
-      <c r="D149" t="n">
+      <c r="D149" t="b">
+        <v>0</v>
+      </c>
+      <c r="E149" t="n">
         <v>1337288</v>
       </c>
-      <c r="E149" t="n">
+      <c r="F149" t="n">
         <v>2410</v>
       </c>
-      <c r="F149" t="n">
-        <v>0</v>
-      </c>
       <c r="G149" t="n">
         <v>0</v>
       </c>
       <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
         <v>609331</v>
-      </c>
-      <c r="I149" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -8985,23 +11452,23 @@
           <t>Husk Jacket Junior</t>
         </is>
       </c>
-      <c r="D150" t="n">
+      <c r="D150" t="b">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
         <v>403642</v>
       </c>
-      <c r="E150" t="n">
+      <c r="F150" t="n">
         <v>784</v>
       </c>
-      <c r="F150" t="n">
+      <c r="G150" t="n">
         <v>469060</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>1195</v>
       </c>
-      <c r="H150" t="n">
+      <c r="I150" t="n">
         <v>605310</v>
-      </c>
-      <c r="I150" t="n">
-        <v>0.833</v>
       </c>
     </row>
     <row r="151">
@@ -9020,23 +11487,23 @@
           <t>Husk Jacket II Junior</t>
         </is>
       </c>
-      <c r="D151" t="n">
-        <v>0</v>
+      <c r="D151" t="b">
+        <v>1</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
       </c>
       <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
         <v>136250</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>240</v>
       </c>
-      <c r="H151" t="n">
+      <c r="I151" t="n">
         <v>605310</v>
-      </c>
-      <c r="I151" t="n">
-        <v>0.167</v>
       </c>
     </row>
     <row r="152">
@@ -9055,23 +11522,23 @@
           <t>Mila II Jacket Women</t>
         </is>
       </c>
-      <c r="D152" t="n">
-        <v>0</v>
+      <c r="D152" t="b">
+        <v>1</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
       </c>
       <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
         <v>439965</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>660</v>
       </c>
-      <c r="H152" t="n">
+      <c r="I152" t="n">
         <v>494678</v>
-      </c>
-      <c r="I152" t="n">
-        <v>0.884</v>
       </c>
     </row>
     <row r="153">
@@ -9090,23 +11557,23 @@
           <t>Mila Jacket Women</t>
         </is>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" t="b">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
         <v>474650</v>
       </c>
-      <c r="E153" t="n">
+      <c r="F153" t="n">
         <v>695</v>
       </c>
-      <c r="F153" t="n">
+      <c r="G153" t="n">
         <v>54713</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>87</v>
       </c>
-      <c r="H153" t="n">
+      <c r="I153" t="n">
         <v>494678</v>
-      </c>
-      <c r="I153" t="n">
-        <v>0.116</v>
       </c>
     </row>
     <row r="154">
@@ -9125,23 +11592,23 @@
           <t>L.I.M Mimic II 3/4 Pant Men</t>
         </is>
       </c>
-      <c r="D154" t="n">
+      <c r="D154" t="b">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
         <v>664</v>
       </c>
-      <c r="E154" t="n">
-        <v>1</v>
-      </c>
       <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="n">
         <v>253642</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>314</v>
       </c>
-      <c r="H154" t="n">
+      <c r="I154" t="n">
         <v>470006</v>
-      </c>
-      <c r="I154" t="n">
-        <v>0.607</v>
       </c>
     </row>
     <row r="155">
@@ -9160,23 +11627,23 @@
           <t>L.I.M Mimic 3/4 Pant Men</t>
         </is>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" t="b">
+        <v>0</v>
+      </c>
+      <c r="E155" t="n">
         <v>402010</v>
       </c>
-      <c r="E155" t="n">
+      <c r="F155" t="n">
         <v>432</v>
       </c>
-      <c r="F155" t="n">
+      <c r="G155" t="n">
         <v>216365</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>203</v>
       </c>
-      <c r="H155" t="n">
+      <c r="I155" t="n">
         <v>470006</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0.393</v>
       </c>
     </row>
     <row r="156">
@@ -9195,23 +11662,23 @@
           <t>L.I.M Down Jacket Women</t>
         </is>
       </c>
-      <c r="D156" t="n">
+      <c r="D156" t="b">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
         <v>582471</v>
       </c>
-      <c r="E156" t="n">
+      <c r="F156" t="n">
         <v>443</v>
       </c>
-      <c r="F156" t="n">
+      <c r="G156" t="n">
         <v>452560</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>419</v>
       </c>
-      <c r="H156" t="n">
+      <c r="I156" t="n">
         <v>455213</v>
-      </c>
-      <c r="I156" t="n">
-        <v>0.991</v>
       </c>
     </row>
     <row r="157">
@@ -9230,23 +11697,23 @@
           <t>L.I.M Down II Jacket Women</t>
         </is>
       </c>
-      <c r="D157" t="n">
-        <v>0</v>
+      <c r="D157" t="b">
+        <v>1</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
       </c>
       <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
         <v>2654</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>4</v>
       </c>
-      <c r="H157" t="n">
+      <c r="I157" t="n">
         <v>455213</v>
-      </c>
-      <c r="I157" t="n">
-        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="158">
@@ -9265,23 +11732,23 @@
           <t>Mid Flex Pant Men</t>
         </is>
       </c>
-      <c r="D158" t="n">
+      <c r="D158" t="b">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
         <v>526007</v>
       </c>
-      <c r="E158" t="n">
+      <c r="F158" t="n">
         <v>916</v>
       </c>
-      <c r="F158" t="n">
+      <c r="G158" t="n">
         <v>436870</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>808</v>
       </c>
-      <c r="H158" t="n">
+      <c r="I158" t="n">
         <v>436870</v>
-      </c>
-      <c r="I158" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -9300,23 +11767,23 @@
           <t>Mid II Flex Pant Men</t>
         </is>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" t="b">
+        <v>1</v>
+      </c>
+      <c r="E159" t="n">
         <v>242</v>
       </c>
-      <c r="E159" t="n">
-        <v>1</v>
-      </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
       </c>
       <c r="H159" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" t="n">
         <v>436870</v>
-      </c>
-      <c r="I159" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -9335,23 +11802,23 @@
           <t>Front Proof Pant Men</t>
         </is>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" t="b">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
         <v>106145</v>
       </c>
-      <c r="E160" t="n">
+      <c r="F160" t="n">
         <v>116</v>
       </c>
-      <c r="F160" t="n">
+      <c r="G160" t="n">
         <v>409235</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>651</v>
       </c>
-      <c r="H160" t="n">
+      <c r="I160" t="n">
         <v>410439</v>
-      </c>
-      <c r="I160" t="n">
-        <v>0.997</v>
       </c>
     </row>
     <row r="161">
@@ -9370,23 +11837,23 @@
           <t>Front Proof II PantMen</t>
         </is>
       </c>
-      <c r="D161" t="n">
-        <v>0</v>
+      <c r="D161" t="b">
+        <v>1</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
       </c>
       <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
         <v>1204</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>2</v>
       </c>
-      <c r="H161" t="n">
+      <c r="I161" t="n">
         <v>410439</v>
-      </c>
-      <c r="I161" t="n">
-        <v>0.003</v>
       </c>
     </row>
     <row r="162">
@@ -9405,23 +11872,23 @@
           <t>L.I.M Mimic 3/4 Pant Women</t>
         </is>
       </c>
-      <c r="D162" t="n">
+      <c r="D162" t="b">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
         <v>238777</v>
       </c>
-      <c r="E162" t="n">
+      <c r="F162" t="n">
         <v>243</v>
       </c>
-      <c r="F162" t="n">
+      <c r="G162" t="n">
         <v>243137</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>300</v>
       </c>
-      <c r="H162" t="n">
+      <c r="I162" t="n">
         <v>384990</v>
-      </c>
-      <c r="I162" t="n">
-        <v>0.634</v>
       </c>
     </row>
     <row r="163">
@@ -9440,23 +11907,23 @@
           <t>L.I.M Mimic II 3/4 Pant Women</t>
         </is>
       </c>
-      <c r="D163" t="n">
+      <c r="D163" t="b">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
         <v>664</v>
       </c>
-      <c r="E163" t="n">
-        <v>1</v>
-      </c>
       <c r="F163" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" t="n">
         <v>141854</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>173</v>
       </c>
-      <c r="H163" t="n">
+      <c r="I163" t="n">
         <v>384990</v>
-      </c>
-      <c r="I163" t="n">
-        <v>0.366</v>
       </c>
     </row>
     <row r="164">
@@ -9475,23 +11942,23 @@
           <t>Husk Pant Junior</t>
         </is>
       </c>
-      <c r="D164" t="n">
+      <c r="D164" t="b">
+        <v>0</v>
+      </c>
+      <c r="E164" t="n">
         <v>206085</v>
       </c>
-      <c r="E164" t="n">
+      <c r="F164" t="n">
         <v>516</v>
       </c>
-      <c r="F164" t="n">
+      <c r="G164" t="n">
         <v>237463</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>943</v>
       </c>
-      <c r="H164" t="n">
+      <c r="I164" t="n">
         <v>338617</v>
-      </c>
-      <c r="I164" t="n">
-        <v>0.789</v>
       </c>
     </row>
     <row r="165">
@@ -9510,23 +11977,23 @@
           <t>Husk Pant II Junior</t>
         </is>
       </c>
-      <c r="D165" t="n">
-        <v>0</v>
+      <c r="D165" t="b">
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
       </c>
       <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
         <v>101154</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>252</v>
       </c>
-      <c r="H165" t="n">
+      <c r="I165" t="n">
         <v>338617</v>
-      </c>
-      <c r="I165" t="n">
-        <v>0.211</v>
       </c>
     </row>
     <row r="166">
@@ -9545,23 +12012,23 @@
           <t>Mimic II Skirt Women</t>
         </is>
       </c>
-      <c r="D166" t="n">
-        <v>0</v>
+      <c r="D166" t="b">
+        <v>1</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
       </c>
       <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
         <v>208160</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>477</v>
       </c>
-      <c r="H166" t="n">
+      <c r="I166" t="n">
         <v>279776</v>
-      </c>
-      <c r="I166" t="n">
-        <v>0.732</v>
       </c>
     </row>
     <row r="167">
@@ -9580,23 +12047,23 @@
           <t>Mimic Skirt Women</t>
         </is>
       </c>
-      <c r="D167" t="n">
+      <c r="D167" t="b">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
         <v>205849</v>
       </c>
-      <c r="E167" t="n">
+      <c r="F167" t="n">
         <v>399</v>
       </c>
-      <c r="F167" t="n">
+      <c r="G167" t="n">
         <v>71616</v>
       </c>
-      <c r="G167" t="n">
+      <c r="H167" t="n">
         <v>175</v>
       </c>
-      <c r="H167" t="n">
+      <c r="I167" t="n">
         <v>279776</v>
-      </c>
-      <c r="I167" t="n">
-        <v>0.268</v>
       </c>
     </row>
     <row r="168">
@@ -9615,23 +12082,23 @@
           <t>Mila Rain II Pant Women</t>
         </is>
       </c>
-      <c r="D168" t="n">
-        <v>0</v>
+      <c r="D168" t="b">
+        <v>1</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
       </c>
       <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="n">
         <v>278611</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>617</v>
       </c>
-      <c r="H168" t="n">
+      <c r="I168" t="n">
         <v>276639</v>
-      </c>
-      <c r="I168" t="n">
-        <v>1.007</v>
       </c>
     </row>
     <row r="169">
@@ -9650,23 +12117,23 @@
           <t>Mila Rain Pant Women</t>
         </is>
       </c>
-      <c r="D169" t="n">
+      <c r="D169" t="b">
+        <v>0</v>
+      </c>
+      <c r="E169" t="n">
         <v>419498</v>
       </c>
-      <c r="E169" t="n">
+      <c r="F169" t="n">
         <v>794</v>
       </c>
-      <c r="F169" t="n">
+      <c r="G169" t="n">
         <v>-1972</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>-4</v>
       </c>
-      <c r="H169" t="n">
+      <c r="I169" t="n">
         <v>276639</v>
-      </c>
-      <c r="I169" t="n">
-        <v>-0.007</v>
       </c>
     </row>
     <row r="170">
@@ -9685,23 +12152,23 @@
           <t>Mila Rain II Pant Men</t>
         </is>
       </c>
-      <c r="D170" t="n">
-        <v>0</v>
+      <c r="D170" t="b">
+        <v>1</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
       </c>
       <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
         <v>265903</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>563</v>
       </c>
-      <c r="H170" t="n">
+      <c r="I170" t="n">
         <v>274331</v>
-      </c>
-      <c r="I170" t="n">
-        <v>0.966</v>
       </c>
     </row>
     <row r="171">
@@ -9720,23 +12187,23 @@
           <t>Mila Rain Pant Men</t>
         </is>
       </c>
-      <c r="D171" t="n">
+      <c r="D171" t="b">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
         <v>403704</v>
       </c>
-      <c r="E171" t="n">
+      <c r="F171" t="n">
         <v>796</v>
       </c>
-      <c r="F171" t="n">
+      <c r="G171" t="n">
         <v>8428</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>20</v>
       </c>
-      <c r="H171" t="n">
+      <c r="I171" t="n">
         <v>274331</v>
-      </c>
-      <c r="I171" t="n">
-        <v>0.034</v>
       </c>
     </row>
     <row r="172">
@@ -9755,23 +12222,23 @@
           <t>L.I.M Mimic Vest Women</t>
         </is>
       </c>
-      <c r="D172" t="n">
+      <c r="D172" t="b">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
         <v>127351</v>
       </c>
-      <c r="E172" t="n">
+      <c r="F172" t="n">
         <v>178</v>
       </c>
-      <c r="F172" t="n">
+      <c r="G172" t="n">
         <v>256562</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>396</v>
       </c>
-      <c r="H172" t="n">
+      <c r="I172" t="n">
         <v>257083</v>
-      </c>
-      <c r="I172" t="n">
-        <v>0.997</v>
       </c>
     </row>
     <row r="173">
@@ -9790,23 +12257,23 @@
           <t>L.I.M Mimic II VestWomen</t>
         </is>
       </c>
-      <c r="D173" t="n">
+      <c r="D173" t="b">
+        <v>1</v>
+      </c>
+      <c r="E173" t="n">
         <v>2151</v>
       </c>
-      <c r="E173" t="n">
+      <c r="F173" t="n">
         <v>3</v>
       </c>
-      <c r="F173" t="n">
+      <c r="G173" t="n">
         <v>521</v>
       </c>
-      <c r="G173" t="n">
-        <v>1</v>
-      </c>
       <c r="H173" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" t="n">
         <v>257083</v>
-      </c>
-      <c r="I173" t="n">
-        <v>0.003</v>
       </c>
     </row>
     <row r="174">
@@ -9825,23 +12292,23 @@
           <t>Aero Pant Men</t>
         </is>
       </c>
-      <c r="D174" t="n">
+      <c r="D174" t="b">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
         <v>354646</v>
       </c>
-      <c r="E174" t="n">
+      <c r="F174" t="n">
         <v>444</v>
       </c>
-      <c r="F174" t="n">
+      <c r="G174" t="n">
         <v>248341</v>
       </c>
-      <c r="G174" t="n">
+      <c r="H174" t="n">
         <v>336</v>
       </c>
-      <c r="H174" t="n">
+      <c r="I174" t="n">
         <v>247542</v>
-      </c>
-      <c r="I174" t="n">
-        <v>1.003</v>
       </c>
     </row>
     <row r="175">
@@ -9860,23 +12327,23 @@
           <t>Aero II Pant Men</t>
         </is>
       </c>
-      <c r="D175" t="n">
-        <v>0</v>
+      <c r="D175" t="b">
+        <v>1</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
       </c>
       <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
         <v>-799</v>
       </c>
-      <c r="G175" t="n">
+      <c r="H175" t="n">
         <v>-1</v>
       </c>
-      <c r="H175" t="n">
+      <c r="I175" t="n">
         <v>247542</v>
-      </c>
-      <c r="I175" t="n">
-        <v>-0.003</v>
       </c>
     </row>
     <row r="176">
@@ -9895,23 +12362,23 @@
           <t>L.I.M ZT Air Base Men</t>
         </is>
       </c>
-      <c r="D176" t="n">
+      <c r="D176" t="b">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
         <v>43652</v>
       </c>
-      <c r="E176" t="n">
+      <c r="F176" t="n">
         <v>64</v>
       </c>
-      <c r="F176" t="n">
+      <c r="G176" t="n">
         <v>96112</v>
       </c>
-      <c r="G176" t="n">
+      <c r="H176" t="n">
         <v>239</v>
       </c>
-      <c r="H176" t="n">
+      <c r="I176" t="n">
         <v>231893</v>
-      </c>
-      <c r="I176" t="n">
-        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="177">
@@ -9930,23 +12397,23 @@
           <t>L.I.M ZT II Air Base Men</t>
         </is>
       </c>
-      <c r="D177" t="n">
-        <v>0</v>
+      <c r="D177" t="b">
+        <v>1</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
         <v>135781</v>
       </c>
-      <c r="G177" t="n">
+      <c r="H177" t="n">
         <v>186</v>
       </c>
-      <c r="H177" t="n">
+      <c r="I177" t="n">
         <v>231893</v>
-      </c>
-      <c r="I177" t="n">
-        <v>0.438</v>
       </c>
     </row>
     <row r="178">
@@ -9965,23 +12432,23 @@
           <t>L.I.M Jacket Women</t>
         </is>
       </c>
-      <c r="D178" t="n">
+      <c r="D178" t="b">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
         <v>277292</v>
       </c>
-      <c r="E178" t="n">
+      <c r="F178" t="n">
         <v>305</v>
       </c>
-      <c r="F178" t="n">
+      <c r="G178" t="n">
         <v>216081</v>
       </c>
-      <c r="G178" t="n">
+      <c r="H178" t="n">
         <v>405</v>
       </c>
-      <c r="H178" t="n">
+      <c r="I178" t="n">
         <v>216081</v>
-      </c>
-      <c r="I178" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="179">
@@ -10000,23 +12467,23 @@
           <t>L.I.M III Jacket Women</t>
         </is>
       </c>
-      <c r="D179" t="n">
+      <c r="D179" t="b">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
         <v>459</v>
       </c>
-      <c r="E179" t="n">
-        <v>1</v>
-      </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
       </c>
       <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
         <v>216081</v>
-      </c>
-      <c r="I179" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
